--- a/FMC Pin Mapping.xlsx
+++ b/FMC Pin Mapping.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3338" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3309" uniqueCount="714">
   <si>
     <t>FMC Connection</t>
   </si>
@@ -717,7 +717,7 @@
     <t>ADC_DCO_N_0</t>
   </si>
   <si>
-    <t>P1_ADC1_SDI</t>
+    <t>P1_ADC1_~CS</t>
   </si>
   <si>
     <t>FMC1_LA_0_P</t>
@@ -750,9 +750,6 @@
     <t>ADC_D0D_N_0</t>
   </si>
   <si>
-    <t>P1_ADC1_~CS</t>
-  </si>
-  <si>
     <t>FMC1_LA_3_P</t>
   </si>
   <si>
@@ -840,7 +837,7 @@
     <t>ADC_D1A_N_1</t>
   </si>
   <si>
-    <t>P1_ADC2_SDI</t>
+    <t>P1_ADC2_~CS</t>
   </si>
   <si>
     <t>FMC1_LA_20_P</t>
@@ -873,9 +870,6 @@
     <t>ADC_D0A_N_1</t>
   </si>
   <si>
-    <t>P1_ADC2_~CS</t>
-  </si>
-  <si>
     <t>FMC1_LA_22_P</t>
   </si>
   <si>
@@ -1125,9 +1119,6 @@
     <t>ADC_D1B_N_0</t>
   </si>
   <si>
-    <t>P1_ADC_Mode_3</t>
-  </si>
-  <si>
     <t>FMC1_LA_7_P</t>
   </si>
   <si>
@@ -1137,9 +1128,6 @@
     <t>ADC_D1B_P_0</t>
   </si>
   <si>
-    <t>P1_ADC_Mode_2</t>
-  </si>
-  <si>
     <t>FMC1_LA_7_N</t>
   </si>
   <si>
@@ -1149,9 +1137,6 @@
     <t>ADC_D1D_N_1</t>
   </si>
   <si>
-    <t>P1_ADC_Mode_1</t>
-  </si>
-  <si>
     <t>FMC1_LA_11_P</t>
   </si>
   <si>
@@ -1161,9 +1146,6 @@
     <t>ADC_D1D_P_1</t>
   </si>
   <si>
-    <t>P1_ADC_Mode_0</t>
-  </si>
-  <si>
     <t>FMC1_LA_11_N</t>
   </si>
   <si>
@@ -1173,9 +1155,6 @@
     <t>ADC_D0C_N_1</t>
   </si>
   <si>
-    <t>P1_ADC_Filter</t>
-  </si>
-  <si>
     <t>FMC1_LA_15_P</t>
   </si>
   <si>
@@ -1233,7 +1212,7 @@
     <t>ADC_D1B_N_1</t>
   </si>
   <si>
-    <t>P1_ADC_~Sync_In</t>
+    <t>P2_AD7768_MCLK+</t>
   </si>
   <si>
     <t>FMC1_LA_21_P</t>
@@ -1245,7 +1224,7 @@
     <t>ADC_D1B_P_1</t>
   </si>
   <si>
-    <t>P1_ADC_~Sync_Out</t>
+    <t>P2_AD7768_MCLK-</t>
   </si>
   <si>
     <t>FMC1_LA_21_N</t>
@@ -1482,12 +1461,18 @@
     <t>PMOD_2_1</t>
   </si>
   <si>
+    <t>ADC3_DO7</t>
+  </si>
+  <si>
     <t>FMC2_LA_18_P</t>
   </si>
   <si>
     <t>PMOD_2_2</t>
   </si>
   <si>
+    <t>ADC3_DO8</t>
+  </si>
+  <si>
     <t>FMC2_LA_18_N</t>
   </si>
   <si>
@@ -1497,7 +1482,7 @@
     <t>P2_PWR_SYNC</t>
   </si>
   <si>
-    <t>ADC3_DO7</t>
+    <t>P2_ADC3_DCLK</t>
   </si>
   <si>
     <t>FMC2_LA_27_P</t>
@@ -1506,21 +1491,15 @@
     <t>P2_PWR_EN</t>
   </si>
   <si>
-    <t>ADC3_DO8</t>
+    <t>P2_ADC3_~DRDY</t>
   </si>
   <si>
     <t>FMC2_LA_27_N</t>
   </si>
   <si>
-    <t>P2_ADC3_DCLK</t>
-  </si>
-  <si>
     <t>I2C_FMC2_SCL</t>
   </si>
   <si>
-    <t>P2_ADC3_~DRDY</t>
-  </si>
-  <si>
     <t>I2C_FMC2_SDA</t>
   </si>
   <si>
@@ -1653,6 +1632,9 @@
     <t>DAC_DCO_N</t>
   </si>
   <si>
+    <t>P2_ADC4_~DRDY</t>
+  </si>
+  <si>
     <t>FMC2_LA_17_N</t>
   </si>
   <si>
@@ -1737,7 +1719,7 @@
     <t>DAC_D_P_12</t>
   </si>
   <si>
-    <t>P2_ADC3_SDI</t>
+    <t>P2_ADC3_~CS</t>
   </si>
   <si>
     <t>FMC2_LA_0_P</t>
@@ -1761,9 +1743,6 @@
     <t>DAC_D_P_11</t>
   </si>
   <si>
-    <t>P2_ADC3_~CS</t>
-  </si>
-  <si>
     <t>FMC2_LA_3_P</t>
   </si>
   <si>
@@ -1887,7 +1866,7 @@
     <t>P2_SDI</t>
   </si>
   <si>
-    <t>P2_ADC4_SDI</t>
+    <t>P2_ADC4_~CS</t>
   </si>
   <si>
     <t>FMC2_LA_29_P</t>
@@ -1908,9 +1887,6 @@
     <t>P2_ADC_CSB_0</t>
   </si>
   <si>
-    <t>P2_ADC4_~CS</t>
-  </si>
-  <si>
     <t>FMC2_LA_31_P</t>
   </si>
   <si>
@@ -1977,105 +1953,87 @@
     <t>DAC_D_P_13</t>
   </si>
   <si>
+    <t>Timing</t>
+  </si>
+  <si>
+    <t>P2_Timing_Input</t>
+  </si>
+  <si>
+    <t>FMC2_LA_2_P</t>
+  </si>
+  <si>
+    <t>AE22</t>
+  </si>
+  <si>
+    <t>DAC_D_N_13</t>
+  </si>
+  <si>
+    <t>FMC2_LA_2_N</t>
+  </si>
+  <si>
+    <t>AF22</t>
+  </si>
+  <si>
+    <t>DAC_D_P_8</t>
+  </si>
+  <si>
+    <t>FMC2_LA_4_P</t>
+  </si>
+  <si>
+    <t>V21</t>
+  </si>
+  <si>
+    <t>DAC_D_N_8</t>
+  </si>
+  <si>
+    <t>FMC2_LA_4_N</t>
+  </si>
+  <si>
+    <t>W21</t>
+  </si>
+  <si>
+    <t>DAC_D_P_7</t>
+  </si>
+  <si>
+    <t>FMC2_LA_7_P</t>
+  </si>
+  <si>
+    <t>AB22</t>
+  </si>
+  <si>
+    <t>DAC_D_N_7</t>
+  </si>
+  <si>
+    <t>FMC2_LA_7_N</t>
+  </si>
+  <si>
+    <t>AC22</t>
+  </si>
+  <si>
+    <t>DAC_D_P_6</t>
+  </si>
+  <si>
+    <t>FMC2_LA_11_P</t>
+  </si>
+  <si>
+    <t>W23</t>
+  </si>
+  <si>
+    <t>DAC_D_N_6</t>
+  </si>
+  <si>
+    <t>FMC2_LA_11_N</t>
+  </si>
+  <si>
+    <t>W24</t>
+  </si>
+  <si>
+    <t>DAC_D_P_5</t>
+  </si>
+  <si>
     <t>Relay Driver</t>
   </si>
   <si>
-    <t>P2_MAX4896_~FLAG1</t>
-  </si>
-  <si>
-    <t>FMC2_LA_2_P</t>
-  </si>
-  <si>
-    <t>AE22</t>
-  </si>
-  <si>
-    <t>DAC_D_N_13</t>
-  </si>
-  <si>
-    <t>P2_MAX4896_~FLAG2</t>
-  </si>
-  <si>
-    <t>FMC2_LA_2_N</t>
-  </si>
-  <si>
-    <t>AF22</t>
-  </si>
-  <si>
-    <t>DAC_D_P_8</t>
-  </si>
-  <si>
-    <t>P2_MAX4896_~FLAG3</t>
-  </si>
-  <si>
-    <t>FMC2_LA_4_P</t>
-  </si>
-  <si>
-    <t>V21</t>
-  </si>
-  <si>
-    <t>DAC_D_N_8</t>
-  </si>
-  <si>
-    <t>P2_MAX4896_~FLAG4</t>
-  </si>
-  <si>
-    <t>FMC2_LA_4_N</t>
-  </si>
-  <si>
-    <t>W21</t>
-  </si>
-  <si>
-    <t>DAC_D_P_7</t>
-  </si>
-  <si>
-    <t>P2_MAX4896_~FLAG5</t>
-  </si>
-  <si>
-    <t>FMC2_LA_7_P</t>
-  </si>
-  <si>
-    <t>AB22</t>
-  </si>
-  <si>
-    <t>DAC_D_N_7</t>
-  </si>
-  <si>
-    <t>P2_MAX4896_~FLAG6</t>
-  </si>
-  <si>
-    <t>FMC2_LA_7_N</t>
-  </si>
-  <si>
-    <t>AC22</t>
-  </si>
-  <si>
-    <t>DAC_D_P_6</t>
-  </si>
-  <si>
-    <t>P2_MAX4896_~FLAG7</t>
-  </si>
-  <si>
-    <t>FMC2_LA_11_P</t>
-  </si>
-  <si>
-    <t>W23</t>
-  </si>
-  <si>
-    <t>DAC_D_N_6</t>
-  </si>
-  <si>
-    <t>P2_MAX4896_~FLAG8</t>
-  </si>
-  <si>
-    <t>FMC2_LA_11_N</t>
-  </si>
-  <si>
-    <t>W24</t>
-  </si>
-  <si>
-    <t>DAC_D_P_5</t>
-  </si>
-  <si>
     <t>P2_MAX4896_Reset</t>
   </si>
   <si>
@@ -2100,28 +2058,31 @@
     <t>P2_DAC_SDO</t>
   </si>
   <si>
+    <t>P2_Relay_ShiftData_DOUT</t>
+  </si>
+  <si>
+    <t>FMC2_LA_19_P</t>
+  </si>
+  <si>
+    <t>K23</t>
+  </si>
+  <si>
+    <t>P2_DAC_CSB</t>
+  </si>
+  <si>
+    <t>P2_Relay_ShiftData</t>
+  </si>
+  <si>
+    <t>FMC2_LA_19_N</t>
+  </si>
+  <si>
+    <t>J23</t>
+  </si>
+  <si>
+    <t>P2_LEuWire/CLKoutDIV_2</t>
+  </si>
+  <si>
     <t>P2_MAX4896_~CS</t>
-  </si>
-  <si>
-    <t>FMC2_LA_19_P</t>
-  </si>
-  <si>
-    <t>K23</t>
-  </si>
-  <si>
-    <t>P2_DAC_CSB</t>
-  </si>
-  <si>
-    <t>P2_Relay_ShiftData</t>
-  </si>
-  <si>
-    <t>FMC2_LA_19_N</t>
-  </si>
-  <si>
-    <t>J23</t>
-  </si>
-  <si>
-    <t>P2_LEuWire/CLKoutDIV_2</t>
   </si>
   <si>
     <t>FMC2_LA_21_P</t>
@@ -2837,8 +2798,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="20.88"/>
-    <col customWidth="1" min="7" max="7" width="17.63"/>
+    <col hidden="1" min="4" max="4" width="12.63"/>
+    <col customWidth="1" hidden="1" min="5" max="5" width="20.88"/>
+    <col hidden="1" min="6" max="6" width="12.63"/>
+    <col customWidth="1" hidden="1" min="7" max="7" width="17.63"/>
     <col customWidth="1" min="9" max="9" width="23.75"/>
     <col customWidth="1" min="11" max="11" width="27.63"/>
   </cols>
@@ -5366,12 +5329,10 @@
       <c r="G68" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="H68" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I68" s="28" t="s">
-        <v>192</v>
-      </c>
+      <c r="H68" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I68" s="14"/>
       <c r="J68" s="24" t="s">
         <v>35</v>
       </c>
@@ -5407,12 +5368,10 @@
       <c r="G69" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="H69" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I69" s="28" t="s">
-        <v>196</v>
-      </c>
+      <c r="H69" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I69" s="14"/>
       <c r="J69" s="24" t="s">
         <v>35</v>
       </c>
@@ -6193,20 +6152,18 @@
       <c r="G91" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="H91" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I91" s="25" t="s">
-        <v>245</v>
-      </c>
+      <c r="H91" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91" s="21"/>
       <c r="J91" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K91" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="L91" s="12" t="s">
         <v>246</v>
-      </c>
-      <c r="L91" s="12" t="s">
-        <v>247</v>
       </c>
       <c r="M91" s="14" t="s">
         <v>38</v>
@@ -6220,19 +6177,19 @@
         <v>13</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D92" s="24" t="s">
         <v>31</v>
       </c>
       <c r="E92" s="25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F92" s="24" t="s">
         <v>31</v>
       </c>
       <c r="G92" s="25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H92" s="20" t="s">
         <v>17</v>
@@ -6242,10 +6199,10 @@
         <v>35</v>
       </c>
       <c r="K92" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="L92" s="12" t="s">
         <v>250</v>
-      </c>
-      <c r="L92" s="12" t="s">
-        <v>251</v>
       </c>
       <c r="M92" s="14" t="s">
         <v>38</v>
@@ -6259,7 +6216,7 @@
         <v>13</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D93" s="15" t="s">
         <v>15</v>
@@ -6302,13 +6259,13 @@
         <v>31</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F94" s="24" t="s">
         <v>31</v>
       </c>
       <c r="G94" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H94" s="20" t="s">
         <v>17</v>
@@ -6318,10 +6275,10 @@
         <v>35</v>
       </c>
       <c r="K94" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="L94" s="12" t="s">
         <v>254</v>
-      </c>
-      <c r="L94" s="12" t="s">
-        <v>255</v>
       </c>
       <c r="M94" s="14" t="s">
         <v>38</v>
@@ -6335,19 +6292,19 @@
         <v>13</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D95" s="24" t="s">
         <v>31</v>
       </c>
       <c r="E95" s="25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F95" s="24" t="s">
         <v>31</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H95" s="20" t="s">
         <v>17</v>
@@ -6357,10 +6314,10 @@
         <v>35</v>
       </c>
       <c r="K95" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="L95" s="12" t="s">
         <v>258</v>
-      </c>
-      <c r="L95" s="12" t="s">
-        <v>259</v>
       </c>
       <c r="M95" s="14" t="s">
         <v>38</v>
@@ -6374,7 +6331,7 @@
         <v>13</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D96" s="15" t="s">
         <v>15</v>
@@ -6411,7 +6368,7 @@
         <v>13</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D97" s="20" t="s">
         <v>17</v>
@@ -6429,10 +6386,10 @@
         <v>35</v>
       </c>
       <c r="K97" s="26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L97" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M97" s="14" t="s">
         <v>38</v>
@@ -6464,10 +6421,10 @@
         <v>35</v>
       </c>
       <c r="K98" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="L98" s="12" t="s">
         <v>263</v>
-      </c>
-      <c r="L98" s="12" t="s">
-        <v>264</v>
       </c>
       <c r="M98" s="14" t="s">
         <v>38</v>
@@ -6518,19 +6475,19 @@
         <v>13</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D100" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E100" s="25" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F100" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G100" s="25" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H100" s="20" t="s">
         <v>17</v>
@@ -6540,10 +6497,10 @@
         <v>35</v>
       </c>
       <c r="K100" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="L100" s="12" t="s">
         <v>267</v>
-      </c>
-      <c r="L100" s="12" t="s">
-        <v>268</v>
       </c>
       <c r="M100" s="14" t="s">
         <v>38</v>
@@ -6557,19 +6514,19 @@
         <v>13</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D101" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E101" s="25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F101" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G101" s="25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H101" s="20" t="s">
         <v>17</v>
@@ -6579,10 +6536,10 @@
         <v>35</v>
       </c>
       <c r="K101" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="L101" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="L101" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="M101" s="14" t="s">
         <v>38</v>
@@ -6596,7 +6553,7 @@
         <v>13</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>15</v>
@@ -6633,34 +6590,34 @@
         <v>13</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D103" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E103" s="25" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F103" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G103" s="25" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H103" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I103" s="25" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J103" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K103" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="L103" s="12" t="s">
         <v>276</v>
-      </c>
-      <c r="L103" s="12" t="s">
-        <v>277</v>
       </c>
       <c r="M103" s="14" t="s">
         <v>76</v>
@@ -6674,34 +6631,34 @@
         <v>13</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D104" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E104" s="25" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F104" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G104" s="25" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H104" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I104" s="25" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J104" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K104" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="L104" s="12" t="s">
         <v>281</v>
-      </c>
-      <c r="L104" s="12" t="s">
-        <v>282</v>
       </c>
       <c r="M104" s="14" t="s">
         <v>76</v>
@@ -6715,7 +6672,7 @@
         <v>13</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D105" s="15" t="s">
         <v>15</v>
@@ -6752,34 +6709,32 @@
         <v>13</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D106" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E106" s="25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F106" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G106" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="H106" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I106" s="25" t="s">
-        <v>286</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="H106" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106" s="21"/>
       <c r="J106" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K106" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L106" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M106" s="14" t="s">
         <v>76</v>
@@ -6793,19 +6748,19 @@
         <v>13</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D107" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E107" s="25" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F107" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G107" s="25" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H107" s="20" t="s">
         <v>17</v>
@@ -6815,10 +6770,10 @@
         <v>35</v>
       </c>
       <c r="K107" s="26" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="L107" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M107" s="14" t="s">
         <v>76</v>
@@ -6832,7 +6787,7 @@
         <v>13</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>15</v>
@@ -6869,34 +6824,32 @@
         <v>13</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D109" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F109" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G109" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="H109" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I109" s="28" t="s">
-        <v>295</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="H109" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I109" s="21"/>
       <c r="J109" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K109" s="26" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L109" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M109" s="14" t="s">
         <v>76</v>
@@ -6910,31 +6863,29 @@
         <v>13</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D110" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F110" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G110" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="H110" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I110" s="28" t="s">
-        <v>298</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="H110" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110" s="21"/>
       <c r="J110" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K110" s="26" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L110" s="12" t="s">
         <v>243</v>
@@ -6951,7 +6902,7 @@
         <v>13</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D111" s="15" t="s">
         <v>15</v>
@@ -6988,34 +6939,32 @@
         <v>13</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D112" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E112" s="28" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F112" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G112" s="28" t="s">
-        <v>302</v>
-      </c>
-      <c r="H112" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I112" s="28" t="s">
-        <v>302</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="H112" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" s="21"/>
       <c r="J112" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K112" s="26" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L112" s="12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M112" s="14" t="s">
         <v>76</v>
@@ -7029,34 +6978,32 @@
         <v>13</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D113" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E113" s="28" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F113" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G113" s="28" t="s">
-        <v>306</v>
-      </c>
-      <c r="H113" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I113" s="28" t="s">
-        <v>306</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="H113" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113" s="21"/>
       <c r="J113" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K113" s="26" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L113" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="M113" s="14" t="s">
         <v>76</v>
@@ -7070,7 +7017,7 @@
         <v>13</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>15</v>
@@ -7107,19 +7054,19 @@
         <v>13</v>
       </c>
       <c r="C115" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="D115" s="35" t="s">
+        <v>309</v>
+      </c>
+      <c r="E115" s="36" t="s">
         <v>310</v>
-      </c>
-      <c r="D115" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="E115" s="36" t="s">
-        <v>312</v>
       </c>
       <c r="F115" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G115" s="34" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H115" s="20" t="s">
         <v>17</v>
@@ -7129,10 +7076,10 @@
         <v>35</v>
       </c>
       <c r="K115" s="26" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="L115" s="12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="M115" s="14" t="s">
         <v>76</v>
@@ -7146,19 +7093,19 @@
         <v>13</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D116" s="35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E116" s="36" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F116" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G116" s="34" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H116" s="20" t="s">
         <v>17</v>
@@ -7168,10 +7115,10 @@
         <v>35</v>
       </c>
       <c r="K116" s="26" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L116" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="M116" s="14" t="s">
         <v>76</v>
@@ -7185,7 +7132,7 @@
         <v>13</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D117" s="15" t="s">
         <v>15</v>
@@ -7222,19 +7169,19 @@
         <v>13</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D118" s="35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E118" s="37" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F118" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G118" s="34" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H118" s="20" t="s">
         <v>17</v>
@@ -7244,10 +7191,10 @@
         <v>35</v>
       </c>
       <c r="K118" s="26" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="L118" s="12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M118" s="14" t="s">
         <v>76</v>
@@ -7261,19 +7208,19 @@
         <v>13</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D119" s="35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E119" s="36" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F119" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G119" s="34" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H119" s="20" t="s">
         <v>17</v>
@@ -7283,10 +7230,10 @@
         <v>35</v>
       </c>
       <c r="K119" s="26" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="L119" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M119" s="14" t="s">
         <v>76</v>
@@ -7300,7 +7247,7 @@
         <v>13</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>15</v>
@@ -7337,31 +7284,31 @@
         <v>13</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D121" s="29" t="s">
         <v>108</v>
       </c>
       <c r="E121" s="30" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F121" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G121" s="30" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H121" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I121" s="30" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J121" s="29" t="s">
         <v>108</v>
       </c>
       <c r="K121" s="31" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L121" s="18"/>
       <c r="M121" s="19"/>
@@ -7374,7 +7321,7 @@
         <v>13</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>15</v>
@@ -7411,7 +7358,7 @@
         <v>13</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D123" s="20" t="s">
         <v>17</v>
@@ -7426,10 +7373,10 @@
       </c>
       <c r="I123" s="21"/>
       <c r="J123" s="22" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K123" s="23" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L123" s="18"/>
       <c r="M123" s="19"/>
@@ -7442,31 +7389,31 @@
         <v>13</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D124" s="27" t="s">
         <v>105</v>
       </c>
       <c r="E124" s="28" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F124" s="27" t="s">
         <v>105</v>
       </c>
       <c r="G124" s="28" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H124" s="27" t="s">
         <v>105</v>
       </c>
       <c r="I124" s="28" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J124" s="22" t="s">
         <v>105</v>
       </c>
       <c r="K124" s="23" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="L124" s="18"/>
       <c r="M124" s="19"/>
@@ -7479,7 +7426,7 @@
         <v>13</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D125" s="15" t="s">
         <v>15</v>
@@ -7516,7 +7463,7 @@
         <v>13</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D126" s="20" t="s">
         <v>17</v>
@@ -7534,10 +7481,10 @@
         <v>18</v>
       </c>
       <c r="K126" s="23" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="L126" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M126" s="14" t="s">
         <v>38</v>
@@ -7551,7 +7498,7 @@
         <v>13</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D127" s="20" t="s">
         <v>17</v>
@@ -7569,10 +7516,10 @@
         <v>18</v>
       </c>
       <c r="K127" s="23" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="L127" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="M127" s="14" t="s">
         <v>38</v>
@@ -7586,7 +7533,7 @@
         <v>13</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D128" s="15" t="s">
         <v>15</v>
@@ -7623,19 +7570,19 @@
         <v>13</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D129" s="24" t="s">
         <v>31</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F129" s="24" t="s">
         <v>31</v>
       </c>
       <c r="G129" s="25" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H129" s="20" t="s">
         <v>17</v>
@@ -7645,10 +7592,10 @@
         <v>35</v>
       </c>
       <c r="K129" s="26" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="L129" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="M129" s="14" t="s">
         <v>38</v>
@@ -7662,19 +7609,19 @@
         <v>13</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D130" s="24" t="s">
         <v>31</v>
       </c>
       <c r="E130" s="25" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F130" s="24" t="s">
         <v>31</v>
       </c>
       <c r="G130" s="25" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H130" s="20" t="s">
         <v>17</v>
@@ -7684,10 +7631,10 @@
         <v>35</v>
       </c>
       <c r="K130" s="26" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L130" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="M130" s="14" t="s">
         <v>38</v>
@@ -7701,7 +7648,7 @@
         <v>13</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D131" s="15" t="s">
         <v>15</v>
@@ -7738,19 +7685,19 @@
         <v>13</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D132" s="24" t="s">
         <v>31</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F132" s="24" t="s">
         <v>31</v>
       </c>
       <c r="G132" s="25" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H132" s="20" t="s">
         <v>17</v>
@@ -7760,10 +7707,10 @@
         <v>35</v>
       </c>
       <c r="K132" s="26" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L132" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="M132" s="14" t="s">
         <v>38</v>
@@ -7777,19 +7724,19 @@
         <v>13</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D133" s="24" t="s">
         <v>31</v>
       </c>
       <c r="E133" s="25" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F133" s="24" t="s">
         <v>31</v>
       </c>
       <c r="G133" s="25" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H133" s="20" t="s">
         <v>17</v>
@@ -7799,10 +7746,10 @@
         <v>35</v>
       </c>
       <c r="K133" s="26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="L133" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M133" s="14" t="s">
         <v>38</v>
@@ -7816,7 +7763,7 @@
         <v>13</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D134" s="15" t="s">
         <v>15</v>
@@ -7853,31 +7800,29 @@
         <v>13</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D135" s="24" t="s">
         <v>31</v>
       </c>
       <c r="E135" s="25" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F135" s="24" t="s">
         <v>31</v>
       </c>
       <c r="G135" s="25" t="s">
-        <v>369</v>
-      </c>
-      <c r="H135" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I135" s="25" t="s">
-        <v>370</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="H135" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" s="21"/>
       <c r="J135" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K135" s="26" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L135" s="12" t="s">
         <v>167</v>
@@ -7894,31 +7839,29 @@
         <v>13</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D136" s="24" t="s">
         <v>31</v>
       </c>
       <c r="E136" s="25" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F136" s="24" t="s">
         <v>31</v>
       </c>
       <c r="G136" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="H136" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I136" s="25" t="s">
-        <v>374</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="H136" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" s="21"/>
       <c r="J136" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K136" s="26" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="L136" s="12" t="s">
         <v>168</v>
@@ -7935,7 +7878,7 @@
         <v>13</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D137" s="15" t="s">
         <v>15</v>
@@ -7978,28 +7921,26 @@
         <v>60</v>
       </c>
       <c r="E138" s="25" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="F138" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G138" s="25" t="s">
-        <v>377</v>
-      </c>
-      <c r="H138" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I138" s="25" t="s">
-        <v>378</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="H138" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" s="21"/>
       <c r="J138" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K138" s="26" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="L138" s="12" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="M138" s="14" t="s">
         <v>38</v>
@@ -8019,28 +7960,26 @@
         <v>60</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F139" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G139" s="25" t="s">
-        <v>381</v>
-      </c>
-      <c r="H139" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I139" s="25" t="s">
-        <v>382</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="H139" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139" s="21"/>
       <c r="J139" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K139" s="26" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="L139" s="12" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="M139" s="14" t="s">
         <v>38</v>
@@ -8091,34 +8030,32 @@
         <v>13</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D141" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F141" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G141" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="H141" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I141" s="25" t="s">
-        <v>386</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="H141" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" s="21"/>
       <c r="J141" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K141" s="26" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="L141" s="12" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="M141" s="14" t="s">
         <v>38</v>
@@ -8132,34 +8069,34 @@
         <v>13</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D142" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E142" s="25" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="F142" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G142" s="25" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="H142" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I142" s="25" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="J142" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K142" s="26" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="L142" s="12" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="M142" s="14" t="s">
         <v>38</v>
@@ -8173,7 +8110,7 @@
         <v>13</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>15</v>
@@ -8210,34 +8147,34 @@
         <v>13</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D144" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E144" s="25" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="F144" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G144" s="25" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="H144" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I144" s="25" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="J144" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K144" s="26" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="L144" s="12" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="M144" s="14" t="s">
         <v>38</v>
@@ -8251,34 +8188,34 @@
         <v>13</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="D145" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E145" s="25" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="F145" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G145" s="25" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="H145" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I145" s="25" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="J145" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K145" s="26" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="L145" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M145" s="14" t="s">
         <v>38</v>
@@ -8292,7 +8229,7 @@
         <v>13</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>15</v>
@@ -8329,31 +8266,31 @@
         <v>13</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D147" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="F147" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G147" s="25" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="H147" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I147" s="25" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="J147" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K147" s="26" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L147" s="12" t="s">
         <v>150</v>
@@ -8370,31 +8307,31 @@
         <v>13</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="D148" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="F148" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G148" s="25" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="H148" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I148" s="25" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="J148" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K148" s="26" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="L148" s="12" t="s">
         <v>149</v>
@@ -8411,7 +8348,7 @@
         <v>13</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="D149" s="15" t="s">
         <v>15</v>
@@ -8448,19 +8385,19 @@
         <v>13</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="D150" s="35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E150" s="36" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="F150" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G150" s="34" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="H150" s="20" t="s">
         <v>17</v>
@@ -8470,10 +8407,10 @@
         <v>35</v>
       </c>
       <c r="K150" s="26" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="L150" s="12" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="M150" s="14" t="s">
         <v>76</v>
@@ -8487,19 +8424,19 @@
         <v>13</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="D151" s="35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E151" s="36" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="F151" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G151" s="34" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="H151" s="20" t="s">
         <v>17</v>
@@ -8509,10 +8446,10 @@
         <v>35</v>
       </c>
       <c r="K151" s="26" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="L151" s="12" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="M151" s="14" t="s">
         <v>76</v>
@@ -8526,7 +8463,7 @@
         <v>13</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="D152" s="15" t="s">
         <v>15</v>
@@ -8563,19 +8500,19 @@
         <v>13</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="D153" s="35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E153" s="36" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="F153" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G153" s="34" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="H153" s="20" t="s">
         <v>17</v>
@@ -8585,10 +8522,10 @@
         <v>35</v>
       </c>
       <c r="K153" s="26" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="L153" s="12" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="M153" s="14" t="s">
         <v>76</v>
@@ -8602,19 +8539,19 @@
         <v>13</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="D154" s="35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E154" s="36" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="F154" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G154" s="34" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="H154" s="20" t="s">
         <v>17</v>
@@ -8624,10 +8561,10 @@
         <v>35</v>
       </c>
       <c r="K154" s="26" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="L154" s="12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="M154" s="14" t="s">
         <v>76</v>
@@ -8641,7 +8578,7 @@
         <v>13</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="D155" s="15" t="s">
         <v>15</v>
@@ -8678,19 +8615,19 @@
         <v>13</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="D156" s="35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E156" s="36" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F156" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G156" s="34" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="H156" s="20" t="s">
         <v>17</v>
@@ -8700,10 +8637,10 @@
         <v>35</v>
       </c>
       <c r="K156" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="L156" s="12" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="M156" s="14" t="s">
         <v>76</v>
@@ -8717,19 +8654,19 @@
         <v>13</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="D157" s="35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E157" s="36" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="F157" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G157" s="34" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="H157" s="20" t="s">
         <v>17</v>
@@ -8739,10 +8676,10 @@
         <v>35</v>
       </c>
       <c r="K157" s="26" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="L157" s="12" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="M157" s="14" t="s">
         <v>76</v>
@@ -8756,7 +8693,7 @@
         <v>13</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="D158" s="15" t="s">
         <v>15</v>
@@ -8793,19 +8730,19 @@
         <v>13</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D159" s="35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E159" s="36" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="F159" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G159" s="34" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="H159" s="20" t="s">
         <v>17</v>
@@ -8815,7 +8752,7 @@
         <v>35</v>
       </c>
       <c r="K159" s="26" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="L159" s="12" t="s">
         <v>46</v>
@@ -8832,19 +8769,19 @@
         <v>13</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="D160" s="35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E160" s="36" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F160" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G160" s="34" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="H160" s="20" t="s">
         <v>17</v>
@@ -8854,7 +8791,7 @@
         <v>35</v>
       </c>
       <c r="K160" s="26" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="L160" s="12" t="s">
         <v>45</v>
@@ -8871,7 +8808,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="D161" s="15" t="s">
         <v>15</v>
@@ -8908,31 +8845,31 @@
         <v>13</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="D162" s="29" t="s">
         <v>108</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F162" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G162" s="30" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H162" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I162" s="30" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J162" s="29" t="s">
         <v>108</v>
       </c>
       <c r="K162" s="31" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L162" s="18"/>
       <c r="M162" s="19"/>
@@ -8942,7 +8879,7 @@
         <v>161.0</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C163" s="14" t="s">
         <v>14</v>
@@ -8979,7 +8916,7 @@
         <v>162.0</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C164" s="14" t="s">
         <v>16</v>
@@ -9000,7 +8937,7 @@
         <v>18</v>
       </c>
       <c r="K164" s="23" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="L164" s="18"/>
       <c r="M164" s="19"/>
@@ -9010,7 +8947,7 @@
         <v>163.0</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C165" s="14" t="s">
         <v>20</v>
@@ -9031,7 +8968,7 @@
         <v>18</v>
       </c>
       <c r="K165" s="23" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="L165" s="18"/>
       <c r="M165" s="19"/>
@@ -9041,7 +8978,7 @@
         <v>164.0</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C166" s="14" t="s">
         <v>22</v>
@@ -9078,7 +9015,7 @@
         <v>165.0</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C167" s="14" t="s">
         <v>23</v>
@@ -9115,7 +9052,7 @@
         <v>166.0</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C168" s="14" t="s">
         <v>24</v>
@@ -9136,7 +9073,7 @@
         <v>18</v>
       </c>
       <c r="K168" s="23" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="L168" s="18"/>
       <c r="M168" s="19"/>
@@ -9146,7 +9083,7 @@
         <v>167.0</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C169" s="14" t="s">
         <v>26</v>
@@ -9167,7 +9104,7 @@
         <v>18</v>
       </c>
       <c r="K169" s="23" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="L169" s="18"/>
       <c r="M169" s="19"/>
@@ -9177,7 +9114,7 @@
         <v>168.0</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C170" s="14" t="s">
         <v>28</v>
@@ -9214,7 +9151,7 @@
         <v>169.0</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C171" s="14" t="s">
         <v>29</v>
@@ -9251,40 +9188,40 @@
         <v>170.0</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C172" s="14" t="s">
         <v>30</v>
       </c>
       <c r="D172" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E172" s="39" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="F172" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G172" s="39" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="H172" s="24" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="I172" s="25" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="J172" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K172" s="26" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="L172" s="12" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="M172" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="173">
@@ -9292,40 +9229,40 @@
         <v>171.0</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C173" s="14" t="s">
         <v>39</v>
       </c>
       <c r="D173" s="38" t="s">
+        <v>453</v>
+      </c>
+      <c r="E173" s="39" t="s">
         <v>460</v>
       </c>
-      <c r="E173" s="39" t="s">
-        <v>467</v>
-      </c>
       <c r="F173" s="38" t="s">
+        <v>453</v>
+      </c>
+      <c r="G173" s="39" t="s">
         <v>460</v>
       </c>
-      <c r="G173" s="39" t="s">
-        <v>467</v>
-      </c>
       <c r="H173" s="24" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="I173" s="25" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="J173" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K173" s="26" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="L173" s="12" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="M173" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="174" hidden="1">
@@ -9333,7 +9270,7 @@
         <v>172.0</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C174" s="14" t="s">
         <v>44</v>
@@ -9370,7 +9307,7 @@
         <v>173.0</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C175" s="14" t="s">
         <v>45</v>
@@ -9407,40 +9344,40 @@
         <v>174.0</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C176" s="14" t="s">
         <v>46</v>
       </c>
       <c r="D176" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="E176" s="39" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="F176" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G176" s="39" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="H176" s="24" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="I176" s="25" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="J176" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K176" s="26" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="L176" s="12" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="M176" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="177">
@@ -9448,40 +9385,40 @@
         <v>175.0</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C177" s="14" t="s">
         <v>52</v>
       </c>
       <c r="D177" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="E177" s="39" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="F177" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G177" s="39" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="H177" s="24" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="I177" s="25" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="J177" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K177" s="26" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="L177" s="12" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="M177" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="178" hidden="1">
@@ -9489,7 +9426,7 @@
         <v>176.0</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C178" s="14" t="s">
         <v>57</v>
@@ -9526,7 +9463,7 @@
         <v>177.0</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C179" s="14" t="s">
         <v>58</v>
@@ -9563,40 +9500,40 @@
         <v>178.0</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C180" s="14" t="s">
         <v>59</v>
       </c>
       <c r="D180" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E180" s="39" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F180" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G180" s="39" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="H180" s="24" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="I180" s="25" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="J180" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K180" s="26" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="L180" s="12" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="M180" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="181">
@@ -9604,40 +9541,40 @@
         <v>179.0</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C181" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D181" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E181" s="39" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="F181" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G181" s="39" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="H181" s="24" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="I181" s="25" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="J181" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K181" s="26" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="L181" s="12" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="M181" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="182" hidden="1">
@@ -9645,7 +9582,7 @@
         <v>180.0</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C182" s="14" t="s">
         <v>70</v>
@@ -9682,7 +9619,7 @@
         <v>181.0</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C183" s="14" t="s">
         <v>71</v>
@@ -9719,7 +9656,7 @@
         <v>182.0</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C184" s="14" t="s">
         <v>72</v>
@@ -9728,28 +9665,28 @@
         <v>84</v>
       </c>
       <c r="E184" s="28" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="F184" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G184" s="28" t="s">
-        <v>488</v>
-      </c>
-      <c r="H184" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I184" s="28" t="s">
-        <v>488</v>
+        <v>481</v>
+      </c>
+      <c r="H184" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="I184" s="25" t="s">
+        <v>482</v>
       </c>
       <c r="J184" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K184" s="26" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="L184" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M184" s="14" t="s">
         <v>38</v>
@@ -9760,7 +9697,7 @@
         <v>183.0</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C185" s="14" t="s">
         <v>77</v>
@@ -9769,28 +9706,28 @@
         <v>84</v>
       </c>
       <c r="E185" s="28" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="F185" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G185" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="H185" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I185" s="28" t="s">
-        <v>490</v>
+        <v>484</v>
+      </c>
+      <c r="H185" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="I185" s="25" t="s">
+        <v>485</v>
       </c>
       <c r="J185" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K185" s="26" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="L185" s="12" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="M185" s="14" t="s">
         <v>38</v>
@@ -9801,7 +9738,7 @@
         <v>184.0</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C186" s="14" t="s">
         <v>81</v>
@@ -9838,7 +9775,7 @@
         <v>185.0</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C187" s="14" t="s">
         <v>82</v>
@@ -9875,7 +9812,7 @@
         <v>186.0</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C188" s="14" t="s">
         <v>83</v>
@@ -9884,28 +9821,28 @@
         <v>108</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F188" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G188" s="30" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="H188" s="24" t="s">
-        <v>462</v>
+        <v>170</v>
       </c>
       <c r="I188" s="25" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="J188" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K188" s="26" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="L188" s="12" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="M188" s="14" t="s">
         <v>38</v>
@@ -9916,7 +9853,7 @@
         <v>187.0</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C189" s="14" t="s">
         <v>88</v>
@@ -9925,28 +9862,28 @@
         <v>108</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="F189" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G189" s="30" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="H189" s="24" t="s">
-        <v>462</v>
+        <v>170</v>
       </c>
       <c r="I189" s="25" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="J189" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K189" s="26" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="L189" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M189" s="14" t="s">
         <v>38</v>
@@ -9957,7 +9894,7 @@
         <v>188.0</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C190" s="14" t="s">
         <v>92</v>
@@ -9994,7 +9931,7 @@
         <v>189.0</v>
       </c>
       <c r="B191" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C191" s="14" t="s">
         <v>93</v>
@@ -10031,7 +9968,7 @@
         <v>190.0</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C192" s="14" t="s">
         <v>94</v>
@@ -10044,17 +9981,15 @@
         <v>17</v>
       </c>
       <c r="G192" s="21"/>
-      <c r="H192" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I192" s="25" t="s">
-        <v>499</v>
-      </c>
+      <c r="H192" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I192" s="21"/>
       <c r="J192" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K192" s="26" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="L192" s="18"/>
       <c r="M192" s="19"/>
@@ -10064,7 +9999,7 @@
         <v>191.0</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C193" s="14" t="s">
         <v>98</v>
@@ -10077,17 +10012,15 @@
         <v>17</v>
       </c>
       <c r="G193" s="21"/>
-      <c r="H193" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I193" s="25" t="s">
-        <v>501</v>
-      </c>
+      <c r="H193" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I193" s="21"/>
       <c r="J193" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K193" s="26" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="L193" s="18"/>
       <c r="M193" s="19"/>
@@ -10097,7 +10030,7 @@
         <v>192.0</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C194" s="14" t="s">
         <v>101</v>
@@ -10134,7 +10067,7 @@
         <v>193.0</v>
       </c>
       <c r="B195" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C195" s="14" t="s">
         <v>102</v>
@@ -10171,7 +10104,7 @@
         <v>194.0</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C196" s="14" t="s">
         <v>103</v>
@@ -10192,7 +10125,7 @@
         <v>105</v>
       </c>
       <c r="K196" s="23" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="L196" s="18"/>
       <c r="M196" s="19"/>
@@ -10202,7 +10135,7 @@
         <v>195.0</v>
       </c>
       <c r="B197" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C197" s="14" t="s">
         <v>107</v>
@@ -10211,25 +10144,25 @@
         <v>108</v>
       </c>
       <c r="E197" s="30" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="F197" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G197" s="30" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="H197" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I197" s="30" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="J197" s="29" t="s">
         <v>108</v>
       </c>
       <c r="K197" s="31" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="L197" s="18"/>
       <c r="M197" s="19"/>
@@ -10239,7 +10172,7 @@
         <v>196.0</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C198" s="14" t="s">
         <v>111</v>
@@ -10276,7 +10209,7 @@
         <v>197.0</v>
       </c>
       <c r="B199" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C199" s="14" t="s">
         <v>112</v>
@@ -10285,25 +10218,25 @@
         <v>108</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="F199" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G199" s="30" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="H199" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I199" s="30" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="J199" s="29" t="s">
         <v>108</v>
       </c>
       <c r="K199" s="31" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="L199" s="18"/>
       <c r="M199" s="19"/>
@@ -10313,7 +10246,7 @@
         <v>198.0</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C200" s="14" t="s">
         <v>113</v>
@@ -10350,7 +10283,7 @@
         <v>199.0</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C201" s="14" t="s">
         <v>114</v>
@@ -10359,19 +10292,19 @@
         <v>108</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="F201" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G201" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="H201" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I201" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="J201" s="29" t="s">
         <v>108</v>
@@ -10387,7 +10320,7 @@
         <v>200.0</v>
       </c>
       <c r="B202" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C202" s="14" t="s">
         <v>116</v>
@@ -10424,7 +10357,7 @@
         <v>201.0</v>
       </c>
       <c r="B203" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C203" s="14" t="s">
         <v>117</v>
@@ -10433,25 +10366,25 @@
         <v>108</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="F203" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G203" s="30" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H203" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I203" s="30" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="J203" s="29" t="s">
         <v>108</v>
       </c>
       <c r="K203" s="32" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="L203" s="18"/>
       <c r="M203" s="19"/>
@@ -10461,7 +10394,7 @@
         <v>202.0</v>
       </c>
       <c r="B204" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C204" s="14" t="s">
         <v>119</v>
@@ -10498,7 +10431,7 @@
         <v>203.0</v>
       </c>
       <c r="B205" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C205" s="14" t="s">
         <v>120</v>
@@ -10535,7 +10468,7 @@
         <v>204.0</v>
       </c>
       <c r="B206" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C206" s="14" t="s">
         <v>121</v>
@@ -10556,7 +10489,7 @@
         <v>18</v>
       </c>
       <c r="K206" s="23" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="L206" s="18"/>
       <c r="M206" s="19"/>
@@ -10566,7 +10499,7 @@
         <v>205.0</v>
       </c>
       <c r="B207" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C207" s="14" t="s">
         <v>123</v>
@@ -10587,7 +10520,7 @@
         <v>18</v>
       </c>
       <c r="K207" s="23" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="L207" s="18"/>
       <c r="M207" s="19"/>
@@ -10597,7 +10530,7 @@
         <v>206.0</v>
       </c>
       <c r="B208" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C208" s="14" t="s">
         <v>125</v>
@@ -10634,7 +10567,7 @@
         <v>207.0</v>
       </c>
       <c r="B209" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C209" s="14" t="s">
         <v>126</v>
@@ -10671,7 +10604,7 @@
         <v>208.0</v>
       </c>
       <c r="B210" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C210" s="14" t="s">
         <v>127</v>
@@ -10685,22 +10618,22 @@
       </c>
       <c r="G210" s="21"/>
       <c r="H210" s="24" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I210" s="25" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="J210" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K210" s="26" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="L210" s="12" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="M210" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="211">
@@ -10708,7 +10641,7 @@
         <v>209.0</v>
       </c>
       <c r="B211" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C211" s="14" t="s">
         <v>133</v>
@@ -10722,22 +10655,22 @@
       </c>
       <c r="G211" s="21"/>
       <c r="H211" s="24" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I211" s="25" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="J211" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K211" s="26" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="L211" s="12" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="M211" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="212" hidden="1">
@@ -10745,7 +10678,7 @@
         <v>210.0</v>
       </c>
       <c r="B212" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C212" s="14" t="s">
         <v>138</v>
@@ -10782,40 +10715,40 @@
         <v>211.0</v>
       </c>
       <c r="B213" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C213" s="14" t="s">
         <v>139</v>
       </c>
       <c r="D213" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E213" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="F213" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G213" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="H213" s="24" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I213" s="25" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="J213" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K213" s="26" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="L213" s="12" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="M213" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="214">
@@ -10823,40 +10756,40 @@
         <v>212.0</v>
       </c>
       <c r="B214" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C214" s="14" t="s">
         <v>144</v>
       </c>
       <c r="D214" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E214" s="39" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="F214" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G214" s="39" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="H214" s="24" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I214" s="25" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="J214" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K214" s="26" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="L214" s="12" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="M214" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="215" hidden="1">
@@ -10864,7 +10797,7 @@
         <v>213.0</v>
       </c>
       <c r="B215" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C215" s="14" t="s">
         <v>149</v>
@@ -10901,40 +10834,40 @@
         <v>214.0</v>
       </c>
       <c r="B216" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C216" s="14" t="s">
         <v>150</v>
       </c>
       <c r="D216" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E216" s="39" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F216" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G216" s="39" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="H216" s="24" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I216" s="25" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="J216" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K216" s="26" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="L216" s="12" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="M216" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="217">
@@ -10942,40 +10875,40 @@
         <v>215.0</v>
       </c>
       <c r="B217" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C217" s="14" t="s">
         <v>155</v>
       </c>
       <c r="D217" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E217" s="39" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="F217" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G217" s="39" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="H217" s="24" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I217" s="25" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="J217" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K217" s="26" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="L217" s="12" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="M217" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" hidden="1">
@@ -10983,7 +10916,7 @@
         <v>216.0</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C218" s="14" t="s">
         <v>160</v>
@@ -11020,40 +10953,40 @@
         <v>217.0</v>
       </c>
       <c r="B219" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C219" s="14" t="s">
         <v>161</v>
       </c>
       <c r="D219" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E219" s="39" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="F219" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G219" s="39" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="H219" s="24" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I219" s="25" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="J219" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K219" s="26" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="L219" s="12" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="M219" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="220">
@@ -11061,40 +10994,40 @@
         <v>218.0</v>
       </c>
       <c r="B220" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C220" s="14" t="s">
         <v>164</v>
       </c>
       <c r="D220" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E220" s="39" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="F220" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G220" s="39" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="H220" s="24" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I220" s="25" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="J220" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K220" s="26" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="L220" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="M220" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="221" hidden="1">
@@ -11102,7 +11035,7 @@
         <v>219.0</v>
       </c>
       <c r="B221" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C221" s="14" t="s">
         <v>167</v>
@@ -11139,37 +11072,37 @@
         <v>220.0</v>
       </c>
       <c r="B222" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C222" s="14" t="s">
         <v>168</v>
       </c>
       <c r="D222" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="E222" s="39" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="F222" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G222" s="39" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="H222" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I222" s="25" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="J222" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K222" s="26" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="L222" s="12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M222" s="14" t="s">
         <v>38</v>
@@ -11180,37 +11113,37 @@
         <v>221.0</v>
       </c>
       <c r="B223" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C223" s="14" t="s">
         <v>174</v>
       </c>
       <c r="D223" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="E223" s="39" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="F223" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G223" s="39" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="H223" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I223" s="25" t="s">
-        <v>501</v>
+        <v>539</v>
       </c>
       <c r="J223" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K223" s="26" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="L223" s="12" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="M223" s="14" t="s">
         <v>38</v>
@@ -11221,7 +11154,7 @@
         <v>222.0</v>
       </c>
       <c r="B224" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C224" s="14" t="s">
         <v>178</v>
@@ -11258,7 +11191,7 @@
         <v>223.0</v>
       </c>
       <c r="B225" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C225" s="14" t="s">
         <v>179</v>
@@ -11267,28 +11200,26 @@
         <v>84</v>
       </c>
       <c r="E225" s="28" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="F225" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G225" s="28" t="s">
-        <v>548</v>
-      </c>
-      <c r="H225" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I225" s="28" t="s">
-        <v>548</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="H225" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I225" s="21"/>
       <c r="J225" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K225" s="26" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="L225" s="12" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="M225" s="14" t="s">
         <v>38</v>
@@ -11299,7 +11230,7 @@
         <v>224.0</v>
       </c>
       <c r="B226" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C226" s="14" t="s">
         <v>185</v>
@@ -11308,28 +11239,26 @@
         <v>84</v>
       </c>
       <c r="E226" s="28" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="F226" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G226" s="28" t="s">
-        <v>550</v>
-      </c>
-      <c r="H226" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I226" s="28" t="s">
-        <v>550</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="H226" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I226" s="21"/>
       <c r="J226" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K226" s="26" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="L226" s="12" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="M226" s="14" t="s">
         <v>38</v>
@@ -11340,7 +11269,7 @@
         <v>225.0</v>
       </c>
       <c r="B227" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C227" s="14" t="s">
         <v>190</v>
@@ -11377,37 +11306,37 @@
         <v>226.0</v>
       </c>
       <c r="B228" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C228" s="14" t="s">
         <v>191</v>
       </c>
       <c r="D228" s="40" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E228" s="41" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="F228" s="40" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="G228" s="41" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="H228" s="40" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="I228" s="41" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="J228" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K228" s="26" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="L228" s="12" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="M228" s="14" t="s">
         <v>38</v>
@@ -11418,37 +11347,37 @@
         <v>227.0</v>
       </c>
       <c r="B229" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C229" s="14" t="s">
         <v>195</v>
       </c>
       <c r="D229" s="40" t="s">
+        <v>546</v>
+      </c>
+      <c r="E229" s="41" t="s">
+        <v>551</v>
+      </c>
+      <c r="F229" s="40" t="s">
+        <v>546</v>
+      </c>
+      <c r="G229" s="41" t="s">
+        <v>551</v>
+      </c>
+      <c r="H229" s="40" t="s">
+        <v>546</v>
+      </c>
+      <c r="I229" s="41" t="s">
         <v>552</v>
-      </c>
-      <c r="E229" s="41" t="s">
-        <v>557</v>
-      </c>
-      <c r="F229" s="40" t="s">
-        <v>552</v>
-      </c>
-      <c r="G229" s="41" t="s">
-        <v>557</v>
-      </c>
-      <c r="H229" s="40" t="s">
-        <v>552</v>
-      </c>
-      <c r="I229" s="41" t="s">
-        <v>558</v>
       </c>
       <c r="J229" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K229" s="26" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="L229" s="12" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="M229" s="14" t="s">
         <v>38</v>
@@ -11459,7 +11388,7 @@
         <v>228.0</v>
       </c>
       <c r="B230" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C230" s="14" t="s">
         <v>199</v>
@@ -11496,7 +11425,7 @@
         <v>229.0</v>
       </c>
       <c r="B231" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C231" s="14" t="s">
         <v>200</v>
@@ -11517,7 +11446,7 @@
         <v>201</v>
       </c>
       <c r="K231" s="23" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="L231" s="18"/>
       <c r="M231" s="19"/>
@@ -11527,7 +11456,7 @@
         <v>230.0</v>
       </c>
       <c r="B232" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C232" s="14" t="s">
         <v>203</v>
@@ -11536,25 +11465,25 @@
         <v>105</v>
       </c>
       <c r="E232" s="28" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="F232" s="27" t="s">
         <v>105</v>
       </c>
       <c r="G232" s="28" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="H232" s="27" t="s">
         <v>105</v>
       </c>
       <c r="I232" s="28" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="J232" s="22" t="s">
         <v>201</v>
       </c>
       <c r="K232" s="23" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="L232" s="18"/>
       <c r="M232" s="19"/>
@@ -11564,7 +11493,7 @@
         <v>231.0</v>
       </c>
       <c r="B233" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C233" s="14" t="s">
         <v>206</v>
@@ -11573,25 +11502,25 @@
         <v>105</v>
       </c>
       <c r="E233" s="28" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="F233" s="27" t="s">
         <v>105</v>
       </c>
       <c r="G233" s="28" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="H233" s="27" t="s">
         <v>105</v>
       </c>
       <c r="I233" s="28" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="J233" s="22" t="s">
         <v>201</v>
       </c>
       <c r="K233" s="23" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="L233" s="18"/>
       <c r="M233" s="19"/>
@@ -11601,7 +11530,7 @@
         <v>232.0</v>
       </c>
       <c r="B234" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C234" s="14" t="s">
         <v>209</v>
@@ -11622,7 +11551,7 @@
         <v>201</v>
       </c>
       <c r="K234" s="23" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="L234" s="18"/>
       <c r="M234" s="19"/>
@@ -11632,7 +11561,7 @@
         <v>233.0</v>
       </c>
       <c r="B235" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C235" s="14" t="s">
         <v>212</v>
@@ -11653,7 +11582,7 @@
         <v>201</v>
       </c>
       <c r="K235" s="23" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="L235" s="18"/>
       <c r="M235" s="19"/>
@@ -11663,7 +11592,7 @@
         <v>234.0</v>
       </c>
       <c r="B236" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C236" s="14" t="s">
         <v>214</v>
@@ -11684,7 +11613,7 @@
         <v>201</v>
       </c>
       <c r="K236" s="23" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="L236" s="18"/>
       <c r="M236" s="19"/>
@@ -11694,7 +11623,7 @@
         <v>235.0</v>
       </c>
       <c r="B237" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C237" s="14" t="s">
         <v>216</v>
@@ -11725,7 +11654,7 @@
         <v>236.0</v>
       </c>
       <c r="B238" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C238" s="14" t="s">
         <v>219</v>
@@ -11734,19 +11663,19 @@
         <v>108</v>
       </c>
       <c r="E238" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="F238" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G238" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="H238" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I238" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="J238" s="29" t="s">
         <v>108</v>
@@ -11762,7 +11691,7 @@
         <v>237.0</v>
       </c>
       <c r="B239" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C239" s="14" t="s">
         <v>220</v>
@@ -11799,7 +11728,7 @@
         <v>238.0</v>
       </c>
       <c r="B240" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C240" s="14" t="s">
         <v>221</v>
@@ -11808,19 +11737,19 @@
         <v>108</v>
       </c>
       <c r="E240" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="F240" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G240" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="H240" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I240" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="J240" s="29" t="s">
         <v>108</v>
@@ -11836,7 +11765,7 @@
         <v>239.0</v>
       </c>
       <c r="B241" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C241" s="14" t="s">
         <v>222</v>
@@ -11873,7 +11802,7 @@
         <v>240.0</v>
       </c>
       <c r="B242" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C242" s="14" t="s">
         <v>223</v>
@@ -11882,19 +11811,19 @@
         <v>108</v>
       </c>
       <c r="E242" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="F242" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G242" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="H242" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I242" s="30" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="J242" s="29" t="s">
         <v>108</v>
@@ -11910,7 +11839,7 @@
         <v>241.0</v>
       </c>
       <c r="B243" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C243" s="14" t="s">
         <v>224</v>
@@ -11947,7 +11876,7 @@
         <v>242.0</v>
       </c>
       <c r="B244" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C244" s="14" t="s">
         <v>225</v>
@@ -11968,10 +11897,10 @@
         <v>18</v>
       </c>
       <c r="K244" s="23" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="L244" s="12" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="M244" s="14" t="s">
         <v>38</v>
@@ -11982,7 +11911,7 @@
         <v>243.0</v>
       </c>
       <c r="B245" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C245" s="14" t="s">
         <v>228</v>
@@ -12003,10 +11932,10 @@
         <v>18</v>
       </c>
       <c r="K245" s="23" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="L245" s="12" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="M245" s="14" t="s">
         <v>38</v>
@@ -12017,7 +11946,7 @@
         <v>244.0</v>
       </c>
       <c r="B246" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C246" s="14" t="s">
         <v>230</v>
@@ -12054,7 +11983,7 @@
         <v>245.0</v>
       </c>
       <c r="B247" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C247" s="14" t="s">
         <v>231</v>
@@ -12091,40 +12020,40 @@
         <v>246.0</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C248" s="14" t="s">
         <v>232</v>
       </c>
       <c r="D248" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E248" s="39" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="F248" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G248" s="39" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="H248" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I248" s="25" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="J248" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K248" s="26" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="L248" s="12" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="M248" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="249">
@@ -12132,40 +12061,40 @@
         <v>247.0</v>
       </c>
       <c r="B249" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C249" s="14" t="s">
         <v>237</v>
       </c>
       <c r="D249" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E249" s="39" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="F249" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G249" s="39" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="H249" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I249" s="25" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="J249" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K249" s="26" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="L249" s="12" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="M249" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="250" hidden="1">
@@ -12173,7 +12102,7 @@
         <v>248.0</v>
       </c>
       <c r="B250" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C250" s="14" t="s">
         <v>242</v>
@@ -12210,40 +12139,38 @@
         <v>249.0</v>
       </c>
       <c r="B251" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C251" s="14" t="s">
         <v>243</v>
       </c>
       <c r="D251" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E251" s="39" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="F251" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G251" s="39" t="s">
-        <v>581</v>
-      </c>
-      <c r="H251" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I251" s="25" t="s">
-        <v>582</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="H251" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I251" s="21"/>
       <c r="J251" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K251" s="26" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="L251" s="12" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="M251" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="252">
@@ -12251,22 +12178,22 @@
         <v>250.0</v>
       </c>
       <c r="B252" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C252" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D252" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E252" s="39" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="F252" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G252" s="39" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="H252" s="20" t="s">
         <v>17</v>
@@ -12276,13 +12203,13 @@
         <v>35</v>
       </c>
       <c r="K252" s="26" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="L252" s="12" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="M252" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="253" hidden="1">
@@ -12290,10 +12217,10 @@
         <v>251.0</v>
       </c>
       <c r="B253" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C253" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D253" s="15" t="s">
         <v>15</v>
@@ -12327,22 +12254,22 @@
         <v>252.0</v>
       </c>
       <c r="B254" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C254" s="14" t="s">
         <v>184</v>
       </c>
       <c r="D254" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E254" s="39" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="F254" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G254" s="39" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="H254" s="20" t="s">
         <v>17</v>
@@ -12352,13 +12279,13 @@
         <v>35</v>
       </c>
       <c r="K254" s="26" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="L254" s="12" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="M254" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="255">
@@ -12366,22 +12293,22 @@
         <v>253.0</v>
       </c>
       <c r="B255" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D255" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E255" s="39" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="F255" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G255" s="39" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="H255" s="20" t="s">
         <v>17</v>
@@ -12391,13 +12318,13 @@
         <v>35</v>
       </c>
       <c r="K255" s="26" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="L255" s="12" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="M255" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="256" hidden="1">
@@ -12405,10 +12332,10 @@
         <v>254.0</v>
       </c>
       <c r="B256" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C256" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" s="15" t="s">
         <v>15</v>
@@ -12442,22 +12369,22 @@
         <v>255.0</v>
       </c>
       <c r="B257" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C257" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D257" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E257" s="39" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="F257" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G257" s="39" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="H257" s="20" t="s">
         <v>17</v>
@@ -12467,13 +12394,13 @@
         <v>35</v>
       </c>
       <c r="K257" s="26" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="L257" s="12" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="M257" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="258">
@@ -12481,22 +12408,22 @@
         <v>256.0</v>
       </c>
       <c r="B258" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C258" s="14" t="s">
         <v>56</v>
       </c>
       <c r="D258" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E258" s="39" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="F258" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G258" s="39" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="H258" s="20" t="s">
         <v>17</v>
@@ -12506,13 +12433,13 @@
         <v>35</v>
       </c>
       <c r="K258" s="26" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="L258" s="12" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="M258" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="259" hidden="1">
@@ -12520,7 +12447,7 @@
         <v>257.0</v>
       </c>
       <c r="B259" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C259" s="14" t="s">
         <v>132</v>
@@ -12557,22 +12484,22 @@
         <v>258.0</v>
       </c>
       <c r="B260" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D260" s="24" t="s">
         <v>170</v>
       </c>
       <c r="E260" s="25" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="F260" s="24" t="s">
         <v>170</v>
       </c>
       <c r="G260" s="25" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="H260" s="20" t="s">
         <v>17</v>
@@ -12582,13 +12509,13 @@
         <v>35</v>
       </c>
       <c r="K260" s="26" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="L260" s="12" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="M260" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="261">
@@ -12596,40 +12523,40 @@
         <v>259.0</v>
       </c>
       <c r="B261" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C261" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D261" s="40" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="E261" s="42" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="F261" s="40" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="G261" s="42" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="H261" s="40" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="I261" s="42" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="J261" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K261" s="26" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="L261" s="12" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="M261" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="262" hidden="1">
@@ -12637,10 +12564,10 @@
         <v>260.0</v>
       </c>
       <c r="B262" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C262" s="14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D262" s="15" t="s">
         <v>15</v>
@@ -12674,37 +12601,35 @@
         <v>261.0</v>
       </c>
       <c r="B263" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C263" s="14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D263" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E263" s="28" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="F263" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G263" s="28" t="s">
-        <v>608</v>
-      </c>
-      <c r="H263" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I263" s="28" t="s">
-        <v>608</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="H263" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I263" s="21"/>
       <c r="J263" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K263" s="26" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="L263" s="12" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="M263" s="14" t="s">
         <v>38</v>
@@ -12715,37 +12640,35 @@
         <v>262.0</v>
       </c>
       <c r="B264" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C264" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D264" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E264" s="28" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="F264" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G264" s="28" t="s">
-        <v>611</v>
-      </c>
-      <c r="H264" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I264" s="28" t="s">
-        <v>611</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="H264" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I264" s="21"/>
       <c r="J264" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K264" s="26" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="L264" s="12" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="M264" s="14" t="s">
         <v>38</v>
@@ -12756,10 +12679,10 @@
         <v>263.0</v>
       </c>
       <c r="B265" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C265" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D265" s="15" t="s">
         <v>15</v>
@@ -12793,37 +12716,37 @@
         <v>264.0</v>
       </c>
       <c r="B266" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C266" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D266" s="40" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E266" s="41" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="F266" s="40" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="G266" s="41" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="H266" s="40" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="I266" s="41" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="J266" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K266" s="26" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="L266" s="12" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="M266" s="14" t="s">
         <v>38</v>
@@ -12834,22 +12757,22 @@
         <v>265.0</v>
       </c>
       <c r="B267" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C267" s="14" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D267" s="12" t="s">
         <v>47</v>
       </c>
       <c r="E267" s="43" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="F267" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G267" s="43" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="H267" s="20" t="s">
         <v>17</v>
@@ -12859,7 +12782,7 @@
         <v>35</v>
       </c>
       <c r="K267" s="26" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="L267" s="12" t="s">
         <v>190</v>
@@ -12873,10 +12796,10 @@
         <v>266.0</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C268" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D268" s="15" t="s">
         <v>15</v>
@@ -12910,34 +12833,32 @@
         <v>267.0</v>
       </c>
       <c r="B269" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C269" s="14" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D269" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E269" s="28" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="F269" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G269" s="28" t="s">
-        <v>619</v>
-      </c>
-      <c r="H269" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I269" s="28" t="s">
-        <v>619</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="H269" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I269" s="21"/>
       <c r="J269" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K269" s="26" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="L269" s="12" t="s">
         <v>179</v>
@@ -12951,34 +12872,32 @@
         <v>268.0</v>
       </c>
       <c r="B270" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C270" s="14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D270" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E270" s="28" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="F270" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G270" s="28" t="s">
-        <v>621</v>
-      </c>
-      <c r="H270" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I270" s="28" t="s">
-        <v>621</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="H270" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I270" s="21"/>
       <c r="J270" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K270" s="26" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="L270" s="12" t="s">
         <v>185</v>
@@ -12992,10 +12911,10 @@
         <v>269.0</v>
       </c>
       <c r="B271" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C271" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D271" s="15" t="s">
         <v>15</v>
@@ -13029,37 +12948,37 @@
         <v>270.0</v>
       </c>
       <c r="B272" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C272" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D272" s="12" t="s">
         <v>47</v>
       </c>
       <c r="E272" s="14" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="F272" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G272" s="14" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="H272" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I272" s="25" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="J272" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K272" s="26" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="L272" s="12" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="M272" s="14" t="s">
         <v>38</v>
@@ -13070,37 +12989,37 @@
         <v>271.0</v>
       </c>
       <c r="B273" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C273" s="14" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D273" s="12" t="s">
         <v>47</v>
       </c>
       <c r="E273" s="14" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="F273" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G273" s="14" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="H273" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I273" s="25" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="J273" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K273" s="26" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="L273" s="12" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="M273" s="14" t="s">
         <v>38</v>
@@ -13111,10 +13030,10 @@
         <v>272.0</v>
       </c>
       <c r="B274" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C274" s="14" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D274" s="15" t="s">
         <v>15</v>
@@ -13148,37 +13067,35 @@
         <v>273.0</v>
       </c>
       <c r="B275" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C275" s="14" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D275" s="24" t="s">
         <v>170</v>
       </c>
       <c r="E275" s="25" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="F275" s="24" t="s">
         <v>170</v>
       </c>
       <c r="G275" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="H275" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I275" s="25" t="s">
-        <v>631</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="H275" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I275" s="21"/>
       <c r="J275" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K275" s="26" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="L275" s="12" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="M275" s="14" t="s">
         <v>38</v>
@@ -13189,22 +13106,22 @@
         <v>274.0</v>
       </c>
       <c r="B276" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C276" s="14" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D276" s="24" t="s">
         <v>170</v>
       </c>
       <c r="E276" s="25" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="F276" s="24" t="s">
         <v>170</v>
       </c>
       <c r="G276" s="25" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="H276" s="20" t="s">
         <v>17</v>
@@ -13214,10 +13131,10 @@
         <v>35</v>
       </c>
       <c r="K276" s="26" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="L276" s="12" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="M276" s="14" t="s">
         <v>38</v>
@@ -13228,10 +13145,10 @@
         <v>275.0</v>
       </c>
       <c r="B277" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C277" s="14" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D277" s="15" t="s">
         <v>15</v>
@@ -13265,22 +13182,22 @@
         <v>276.0</v>
       </c>
       <c r="B278" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C278" s="14" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D278" s="24" t="s">
         <v>170</v>
       </c>
       <c r="E278" s="25" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="F278" s="24" t="s">
         <v>170</v>
       </c>
       <c r="G278" s="25" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="H278" s="20" t="s">
         <v>17</v>
@@ -13290,7 +13207,7 @@
         <v>35</v>
       </c>
       <c r="K278" s="26" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="L278" s="12" t="s">
         <v>71</v>
@@ -13304,37 +13221,37 @@
         <v>277.0</v>
       </c>
       <c r="B279" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C279" s="14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D279" s="40" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="E279" s="42" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="F279" s="40" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="G279" s="42" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="H279" s="40" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="I279" s="42" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="J279" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K279" s="26" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="L279" s="12" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="M279" s="14" t="s">
         <v>38</v>
@@ -13345,10 +13262,10 @@
         <v>278.0</v>
       </c>
       <c r="B280" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C280" s="14" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D280" s="15" t="s">
         <v>15</v>
@@ -13382,34 +13299,34 @@
         <v>279.0</v>
       </c>
       <c r="B281" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C281" s="14" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D281" s="29" t="s">
         <v>108</v>
       </c>
       <c r="E281" s="30" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="F281" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G281" s="30" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="H281" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I281" s="30" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="J281" s="29" t="s">
         <v>108</v>
       </c>
       <c r="K281" s="31" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L281" s="18"/>
       <c r="M281" s="19"/>
@@ -13419,10 +13336,10 @@
         <v>280.0</v>
       </c>
       <c r="B282" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C282" s="14" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D282" s="15" t="s">
         <v>15</v>
@@ -13456,10 +13373,10 @@
         <v>281.0</v>
       </c>
       <c r="B283" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C283" s="14" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D283" s="20" t="s">
         <v>17</v>
@@ -13474,10 +13391,10 @@
       </c>
       <c r="I283" s="21"/>
       <c r="J283" s="22" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K283" s="23" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="L283" s="18"/>
       <c r="M283" s="19"/>
@@ -13487,34 +13404,34 @@
         <v>282.0</v>
       </c>
       <c r="B284" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D284" s="27" t="s">
         <v>105</v>
       </c>
       <c r="E284" s="28" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="F284" s="27" t="s">
         <v>105</v>
       </c>
       <c r="G284" s="28" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="H284" s="27" t="s">
         <v>105</v>
       </c>
       <c r="I284" s="28" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="J284" s="22" t="s">
         <v>105</v>
       </c>
       <c r="K284" s="23" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="L284" s="18"/>
       <c r="M284" s="19"/>
@@ -13524,10 +13441,10 @@
         <v>283.0</v>
       </c>
       <c r="B285" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C285" s="14" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D285" s="15" t="s">
         <v>15</v>
@@ -13561,22 +13478,22 @@
         <v>284.0</v>
       </c>
       <c r="B286" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D286" s="12" t="s">
         <v>47</v>
       </c>
       <c r="E286" s="14" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="F286" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G286" s="14" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="H286" s="20" t="s">
         <v>17</v>
@@ -13586,13 +13503,13 @@
         <v>18</v>
       </c>
       <c r="K286" s="23" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="L286" s="12" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="M286" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="287">
@@ -13600,22 +13517,22 @@
         <v>285.0</v>
       </c>
       <c r="B287" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C287" s="14" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D287" s="12" t="s">
         <v>47</v>
       </c>
       <c r="E287" s="14" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="F287" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G287" s="14" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="H287" s="20" t="s">
         <v>17</v>
@@ -13625,13 +13542,13 @@
         <v>18</v>
       </c>
       <c r="K287" s="23" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="L287" s="12" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="M287" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="288" hidden="1">
@@ -13639,10 +13556,10 @@
         <v>286.0</v>
       </c>
       <c r="B288" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C288" s="14" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D288" s="15" t="s">
         <v>15</v>
@@ -13676,40 +13593,40 @@
         <v>287.0</v>
       </c>
       <c r="B289" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C289" s="14" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D289" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E289" s="39" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="F289" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G289" s="39" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="H289" s="44" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="I289" s="45" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="J289" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K289" s="26" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="L289" s="12" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="M289" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="290">
@@ -13717,40 +13634,38 @@
         <v>288.0</v>
       </c>
       <c r="B290" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C290" s="14" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D290" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E290" s="39" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="F290" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G290" s="39" t="s">
-        <v>658</v>
-      </c>
-      <c r="H290" s="44" t="s">
-        <v>654</v>
-      </c>
-      <c r="I290" s="45" t="s">
-        <v>659</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="H290" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I290" s="21"/>
       <c r="J290" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K290" s="26" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="L290" s="12" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="M290" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="291" hidden="1">
@@ -13758,10 +13673,10 @@
         <v>289.0</v>
       </c>
       <c r="B291" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C291" s="14" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D291" s="15" t="s">
         <v>15</v>
@@ -13795,40 +13710,38 @@
         <v>290.0</v>
       </c>
       <c r="B292" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C292" s="14" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D292" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E292" s="39" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="F292" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G292" s="39" t="s">
-        <v>662</v>
-      </c>
-      <c r="H292" s="44" t="s">
-        <v>654</v>
-      </c>
-      <c r="I292" s="45" t="s">
-        <v>663</v>
-      </c>
+        <v>653</v>
+      </c>
+      <c r="H292" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I292" s="21"/>
       <c r="J292" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K292" s="26" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="L292" s="12" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="M292" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="293">
@@ -13836,40 +13749,38 @@
         <v>291.0</v>
       </c>
       <c r="B293" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C293" s="14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D293" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E293" s="39" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="F293" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G293" s="39" t="s">
-        <v>666</v>
-      </c>
-      <c r="H293" s="44" t="s">
-        <v>654</v>
-      </c>
-      <c r="I293" s="45" t="s">
-        <v>667</v>
-      </c>
+        <v>656</v>
+      </c>
+      <c r="H293" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I293" s="21"/>
       <c r="J293" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K293" s="26" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="L293" s="12" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="M293" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="294" hidden="1">
@@ -13877,10 +13788,10 @@
         <v>292.0</v>
       </c>
       <c r="B294" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C294" s="14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D294" s="15" t="s">
         <v>15</v>
@@ -13914,40 +13825,38 @@
         <v>293.0</v>
       </c>
       <c r="B295" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C295" s="14" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D295" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E295" s="39" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="F295" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G295" s="39" t="s">
-        <v>670</v>
-      </c>
-      <c r="H295" s="44" t="s">
-        <v>654</v>
-      </c>
-      <c r="I295" s="45" t="s">
-        <v>671</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="H295" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I295" s="21"/>
       <c r="J295" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K295" s="26" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="L295" s="12" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="M295" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="296">
@@ -13955,40 +13864,38 @@
         <v>294.0</v>
       </c>
       <c r="B296" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C296" s="14" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D296" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E296" s="39" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="F296" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G296" s="39" t="s">
-        <v>674</v>
-      </c>
-      <c r="H296" s="44" t="s">
-        <v>654</v>
-      </c>
-      <c r="I296" s="45" t="s">
-        <v>675</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="H296" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I296" s="21"/>
       <c r="J296" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K296" s="26" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="L296" s="12" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="M296" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="297" hidden="1">
@@ -13996,10 +13903,10 @@
         <v>295.0</v>
       </c>
       <c r="B297" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C297" s="14" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D297" s="15" t="s">
         <v>15</v>
@@ -14033,40 +13940,38 @@
         <v>296.0</v>
       </c>
       <c r="B298" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C298" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D298" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E298" s="39" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="F298" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G298" s="39" t="s">
-        <v>678</v>
-      </c>
-      <c r="H298" s="44" t="s">
-        <v>654</v>
-      </c>
-      <c r="I298" s="45" t="s">
-        <v>679</v>
-      </c>
+        <v>665</v>
+      </c>
+      <c r="H298" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I298" s="21"/>
       <c r="J298" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K298" s="26" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="L298" s="12" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="M298" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="299">
@@ -14074,40 +13979,38 @@
         <v>297.0</v>
       </c>
       <c r="B299" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C299" s="14" t="s">
         <v>236</v>
       </c>
       <c r="D299" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E299" s="39" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="F299" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G299" s="39" t="s">
-        <v>682</v>
-      </c>
-      <c r="H299" s="44" t="s">
-        <v>654</v>
-      </c>
-      <c r="I299" s="45" t="s">
-        <v>683</v>
-      </c>
+        <v>668</v>
+      </c>
+      <c r="H299" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I299" s="21"/>
       <c r="J299" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K299" s="26" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="L299" s="12" t="s">
-        <v>685</v>
+        <v>670</v>
       </c>
       <c r="M299" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="300" hidden="1">
@@ -14115,7 +14018,7 @@
         <v>298.0</v>
       </c>
       <c r="B300" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C300" s="14" t="s">
         <v>241</v>
@@ -14152,40 +14055,40 @@
         <v>299.0</v>
       </c>
       <c r="B301" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C301" s="14" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D301" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E301" s="39" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="F301" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G301" s="39" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="H301" s="44" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="I301" s="45" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="J301" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K301" s="26" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="L301" s="12" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="M301" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="302">
@@ -14193,40 +14096,40 @@
         <v>300.0</v>
       </c>
       <c r="B302" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C302" s="14" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D302" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E302" s="39" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="F302" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="G302" s="39" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="H302" s="44" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="I302" s="45" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="J302" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K302" s="26" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="L302" s="12" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="M302" s="14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="303" hidden="1">
@@ -14234,10 +14137,10 @@
         <v>301.0</v>
       </c>
       <c r="B303" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C303" s="14" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D303" s="15" t="s">
         <v>15</v>
@@ -14271,37 +14174,37 @@
         <v>302.0</v>
       </c>
       <c r="B304" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C304" s="14" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D304" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="E304" s="39" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="F304" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G304" s="39" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="H304" s="44" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="I304" s="45" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="J304" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K304" s="26" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="L304" s="12" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="M304" s="14" t="s">
         <v>38</v>
@@ -14312,37 +14215,37 @@
         <v>303.0</v>
       </c>
       <c r="B305" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C305" s="14" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="D305" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="E305" s="39" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="F305" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G305" s="39" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="H305" s="44" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="I305" s="45" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="J305" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K305" s="26" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="L305" s="12" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="M305" s="14" t="s">
         <v>38</v>
@@ -14353,10 +14256,10 @@
         <v>304.0</v>
       </c>
       <c r="B306" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C306" s="14" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="D306" s="15" t="s">
         <v>15</v>
@@ -14390,35 +14293,37 @@
         <v>305.0</v>
       </c>
       <c r="B307" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C307" s="14" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D307" s="12" t="s">
         <v>47</v>
       </c>
       <c r="E307" s="43" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="F307" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G307" s="43" t="s">
-        <v>702</v>
-      </c>
-      <c r="H307" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="I307" s="21"/>
+        <v>688</v>
+      </c>
+      <c r="H307" s="44" t="s">
+        <v>672</v>
+      </c>
+      <c r="I307" s="45" t="s">
+        <v>689</v>
+      </c>
       <c r="J307" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K307" s="26" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="L307" s="12" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="M307" s="14" t="s">
         <v>38</v>
@@ -14429,22 +14334,22 @@
         <v>306.0</v>
       </c>
       <c r="B308" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C308" s="14" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="D308" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="E308" s="39" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="F308" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G308" s="39" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="H308" s="20" t="s">
         <v>17</v>
@@ -14454,10 +14359,10 @@
         <v>35</v>
       </c>
       <c r="K308" s="26" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="L308" s="12" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="M308" s="14" t="s">
         <v>38</v>
@@ -14468,10 +14373,10 @@
         <v>307.0</v>
       </c>
       <c r="B309" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C309" s="14" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="D309" s="15" t="s">
         <v>15</v>
@@ -14505,37 +14410,37 @@
         <v>308.0</v>
       </c>
       <c r="B310" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C310" s="14" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="D310" s="40" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="E310" s="42" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="F310" s="40" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="G310" s="42" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="H310" s="40" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="I310" s="42" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="J310" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K310" s="26" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="L310" s="12" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="M310" s="14" t="s">
         <v>38</v>
@@ -14546,37 +14451,37 @@
         <v>309.0</v>
       </c>
       <c r="B311" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C311" s="14" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="D311" s="40" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="E311" s="42" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="F311" s="40" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="G311" s="42" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="H311" s="40" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="I311" s="42" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="J311" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K311" s="26" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="L311" s="12" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="M311" s="14" t="s">
         <v>38</v>
@@ -14587,10 +14492,10 @@
         <v>310.0</v>
       </c>
       <c r="B312" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C312" s="14" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="D312" s="15" t="s">
         <v>15</v>
@@ -14624,22 +14529,22 @@
         <v>311.0</v>
       </c>
       <c r="B313" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C313" s="14" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="D313" s="24" t="s">
         <v>170</v>
       </c>
       <c r="E313" s="25" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="F313" s="24" t="s">
         <v>170</v>
       </c>
       <c r="G313" s="25" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="H313" s="20" t="s">
         <v>17</v>
@@ -14649,10 +14554,10 @@
         <v>35</v>
       </c>
       <c r="K313" s="26" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="L313" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="M313" s="14" t="s">
         <v>38</v>
@@ -14663,22 +14568,22 @@
         <v>312.0</v>
       </c>
       <c r="B314" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C314" s="14" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="D314" s="24" t="s">
         <v>170</v>
       </c>
       <c r="E314" s="25" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="F314" s="24" t="s">
         <v>170</v>
       </c>
       <c r="G314" s="25" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="H314" s="20" t="s">
         <v>17</v>
@@ -14688,10 +14593,10 @@
         <v>35</v>
       </c>
       <c r="K314" s="26" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="L314" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M314" s="14" t="s">
         <v>38</v>
@@ -14702,10 +14607,10 @@
         <v>313.0</v>
       </c>
       <c r="B315" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C315" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="D315" s="15" t="s">
         <v>15</v>
@@ -14739,16 +14644,16 @@
         <v>314.0</v>
       </c>
       <c r="B316" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C316" s="14" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="D316" s="35" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="E316" s="36" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="F316" s="20" t="s">
         <v>17</v>
@@ -14762,7 +14667,7 @@
         <v>35</v>
       </c>
       <c r="K316" s="26" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="L316" s="12" t="s">
         <v>191</v>
@@ -14776,16 +14681,16 @@
         <v>315.0</v>
       </c>
       <c r="B317" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C317" s="14" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="D317" s="35" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="E317" s="36" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="F317" s="20" t="s">
         <v>17</v>
@@ -14799,7 +14704,7 @@
         <v>35</v>
       </c>
       <c r="K317" s="26" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="L317" s="12" t="s">
         <v>83</v>
@@ -14813,10 +14718,10 @@
         <v>316.0</v>
       </c>
       <c r="B318" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C318" s="14" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="D318" s="15" t="s">
         <v>15</v>
@@ -14850,10 +14755,10 @@
         <v>317.0</v>
       </c>
       <c r="B319" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C319" s="14" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D319" s="20" t="s">
         <v>17</v>
@@ -14871,10 +14776,10 @@
         <v>35</v>
       </c>
       <c r="K319" s="26" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="L319" s="12" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="M319" s="14" t="s">
         <v>38</v>
@@ -14885,10 +14790,10 @@
         <v>318.0</v>
       </c>
       <c r="B320" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C320" s="14" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="D320" s="20" t="s">
         <v>17</v>
@@ -14906,10 +14811,10 @@
         <v>35</v>
       </c>
       <c r="K320" s="26" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="L320" s="12" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="M320" s="14" t="s">
         <v>38</v>
@@ -14920,10 +14825,10 @@
         <v>319.0</v>
       </c>
       <c r="B321" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C321" s="14" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="D321" s="15" t="s">
         <v>15</v>
@@ -14957,34 +14862,34 @@
         <v>320.0</v>
       </c>
       <c r="B322" s="47" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C322" s="48" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="D322" s="49" t="s">
         <v>108</v>
       </c>
       <c r="E322" s="50" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="F322" s="49" t="s">
         <v>108</v>
       </c>
       <c r="G322" s="50" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="H322" s="49" t="s">
         <v>108</v>
       </c>
       <c r="I322" s="50" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="J322" s="49" t="s">
         <v>108</v>
       </c>
       <c r="K322" s="51" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L322" s="52"/>
       <c r="M322" s="53"/>
@@ -15004,6 +14909,7 @@
         <filter val="PMOD"/>
         <filter val="Slow ADC Ctrl"/>
         <filter val="Present"/>
+        <filter val="Timing"/>
         <filter val="AD7794"/>
         <filter val="Power"/>
         <filter val="AMC7923"/>

--- a/FMC Pin Mapping.xlsx
+++ b/FMC Pin Mapping.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3309" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3307" uniqueCount="714">
   <si>
     <t>FMC Connection</t>
   </si>
@@ -1155,6 +1155,9 @@
     <t>ADC_D0C_N_1</t>
   </si>
   <si>
+    <t>P1_AD7768_SDI</t>
+  </si>
+  <si>
     <t>FMC1_LA_15_P</t>
   </si>
   <si>
@@ -1212,7 +1215,7 @@
     <t>ADC_D1B_N_1</t>
   </si>
   <si>
-    <t>P2_AD7768_MCLK+</t>
+    <t>P1_AD7768_MCLK+</t>
   </si>
   <si>
     <t>FMC1_LA_21_P</t>
@@ -1224,7 +1227,7 @@
     <t>ADC_D1B_P_1</t>
   </si>
   <si>
-    <t>P2_AD7768_MCLK-</t>
+    <t>P1_AD7768_MCLK-</t>
   </si>
   <si>
     <t>FMC1_LA_21_N</t>
@@ -1242,6 +1245,9 @@
     <t>AD7606C_DoutE</t>
   </si>
   <si>
+    <t>P1_ValidCLK</t>
+  </si>
+  <si>
     <t>FMC1_LA_24_P</t>
   </si>
   <si>
@@ -1659,9 +1665,6 @@
     <t>P2_AD7794_CSb</t>
   </si>
   <si>
-    <t>P2_AD7794_~CS</t>
-  </si>
-  <si>
     <t>FMC2_LA_26_P</t>
   </si>
   <si>
@@ -1671,9 +1674,6 @@
     <t>P2_AD7794_DOUT/RDYb</t>
   </si>
   <si>
-    <t>P2_AD7794_DOUT</t>
-  </si>
-  <si>
     <t>FMC2_LA_26_N</t>
   </si>
   <si>
@@ -1809,7 +1809,7 @@
     <t>P2_POLL_SCLK</t>
   </si>
   <si>
-    <t>P2_AUX_SCLK</t>
+    <t>P2_AMC7823_SPI_SCLK</t>
   </si>
   <si>
     <t>FMC2_LA_16_N</t>
@@ -1911,7 +1911,7 @@
     <t>P2_POLL_MOSI</t>
   </si>
   <si>
-    <t>P2_AUX_MOSI</t>
+    <t>P2_AMC7823_SPI_MOSI</t>
   </si>
   <si>
     <t>FMC2_LA_33_N</t>
@@ -2798,10 +2798,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col hidden="1" min="4" max="4" width="12.63"/>
-    <col customWidth="1" hidden="1" min="5" max="5" width="20.88"/>
-    <col hidden="1" min="6" max="6" width="12.63"/>
-    <col customWidth="1" hidden="1" min="7" max="7" width="17.63"/>
+    <col customWidth="1" min="5" max="5" width="20.88"/>
+    <col customWidth="1" min="7" max="7" width="17.63"/>
     <col customWidth="1" min="9" max="9" width="23.75"/>
     <col customWidth="1" min="11" max="11" width="27.63"/>
   </cols>
@@ -3829,12 +3827,10 @@
       <c r="G28" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="H28" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I28" s="28" t="s">
-        <v>85</v>
-      </c>
+      <c r="H28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="21"/>
       <c r="J28" s="24" t="s">
         <v>35</v>
       </c>
@@ -3870,12 +3866,10 @@
       <c r="G29" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="H29" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="I29" s="28" t="s">
-        <v>89</v>
-      </c>
+      <c r="H29" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="21"/>
       <c r="J29" s="24" t="s">
         <v>35</v>
       </c>
@@ -8044,18 +8038,20 @@
       <c r="G141" s="25" t="s">
         <v>379</v>
       </c>
-      <c r="H141" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="I141" s="21"/>
+      <c r="H141" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="I141" s="25" t="s">
+        <v>380</v>
+      </c>
       <c r="J141" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K141" s="26" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L141" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M141" s="14" t="s">
         <v>38</v>
@@ -8069,34 +8065,34 @@
         <v>13</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D142" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E142" s="25" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F142" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G142" s="25" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H142" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I142" s="25" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J142" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K142" s="26" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L142" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M142" s="14" t="s">
         <v>38</v>
@@ -8110,7 +8106,7 @@
         <v>13</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>15</v>
@@ -8147,31 +8143,31 @@
         <v>13</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D144" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E144" s="25" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F144" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G144" s="25" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H144" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I144" s="25" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J144" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K144" s="26" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L144" s="12" t="s">
         <v>369</v>
@@ -8188,31 +8184,31 @@
         <v>13</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D145" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E145" s="25" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F145" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G145" s="25" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H145" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I145" s="25" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J145" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K145" s="26" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L145" s="12" t="s">
         <v>259</v>
@@ -8229,7 +8225,7 @@
         <v>13</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>15</v>
@@ -8266,31 +8262,31 @@
         <v>13</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D147" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F147" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G147" s="25" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H147" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I147" s="25" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J147" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K147" s="26" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L147" s="12" t="s">
         <v>150</v>
@@ -8307,31 +8303,31 @@
         <v>13</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D148" s="24" t="s">
         <v>60</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F148" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G148" s="25" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H148" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I148" s="25" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J148" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K148" s="26" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L148" s="12" t="s">
         <v>149</v>
@@ -8348,7 +8344,7 @@
         <v>13</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D149" s="15" t="s">
         <v>15</v>
@@ -8385,32 +8381,34 @@
         <v>13</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D150" s="35" t="s">
         <v>309</v>
       </c>
       <c r="E150" s="36" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F150" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G150" s="34" t="s">
-        <v>408</v>
-      </c>
-      <c r="H150" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="I150" s="21"/>
+        <v>409</v>
+      </c>
+      <c r="H150" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="I150" s="25" t="s">
+        <v>410</v>
+      </c>
       <c r="J150" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K150" s="26" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L150" s="12" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M150" s="14" t="s">
         <v>76</v>
@@ -8424,19 +8422,19 @@
         <v>13</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D151" s="35" t="s">
         <v>309</v>
       </c>
       <c r="E151" s="36" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F151" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G151" s="34" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H151" s="20" t="s">
         <v>17</v>
@@ -8446,10 +8444,10 @@
         <v>35</v>
       </c>
       <c r="K151" s="26" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L151" s="12" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M151" s="14" t="s">
         <v>76</v>
@@ -8463,7 +8461,7 @@
         <v>13</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D152" s="15" t="s">
         <v>15</v>
@@ -8500,19 +8498,19 @@
         <v>13</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D153" s="35" t="s">
         <v>309</v>
       </c>
       <c r="E153" s="36" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F153" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G153" s="34" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H153" s="20" t="s">
         <v>17</v>
@@ -8522,10 +8520,10 @@
         <v>35</v>
       </c>
       <c r="K153" s="26" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L153" s="12" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M153" s="14" t="s">
         <v>76</v>
@@ -8539,19 +8537,19 @@
         <v>13</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D154" s="35" t="s">
         <v>309</v>
       </c>
       <c r="E154" s="36" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F154" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G154" s="34" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H154" s="20" t="s">
         <v>17</v>
@@ -8561,7 +8559,7 @@
         <v>35</v>
       </c>
       <c r="K154" s="26" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L154" s="12" t="s">
         <v>366</v>
@@ -8578,7 +8576,7 @@
         <v>13</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D155" s="15" t="s">
         <v>15</v>
@@ -8615,19 +8613,19 @@
         <v>13</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D156" s="35" t="s">
         <v>309</v>
       </c>
       <c r="E156" s="36" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F156" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G156" s="34" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H156" s="20" t="s">
         <v>17</v>
@@ -8637,10 +8635,10 @@
         <v>35</v>
       </c>
       <c r="K156" s="26" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L156" s="12" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M156" s="14" t="s">
         <v>76</v>
@@ -8654,19 +8652,19 @@
         <v>13</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D157" s="35" t="s">
         <v>309</v>
       </c>
       <c r="E157" s="36" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F157" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G157" s="34" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H157" s="20" t="s">
         <v>17</v>
@@ -8676,10 +8674,10 @@
         <v>35</v>
       </c>
       <c r="K157" s="26" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L157" s="12" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M157" s="14" t="s">
         <v>76</v>
@@ -8693,7 +8691,7 @@
         <v>13</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D158" s="15" t="s">
         <v>15</v>
@@ -8730,19 +8728,19 @@
         <v>13</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D159" s="35" t="s">
         <v>309</v>
       </c>
       <c r="E159" s="36" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F159" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G159" s="34" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H159" s="20" t="s">
         <v>17</v>
@@ -8752,7 +8750,7 @@
         <v>35</v>
       </c>
       <c r="K159" s="26" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L159" s="12" t="s">
         <v>46</v>
@@ -8769,19 +8767,19 @@
         <v>13</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D160" s="35" t="s">
         <v>309</v>
       </c>
       <c r="E160" s="36" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F160" s="33" t="s">
         <v>180</v>
       </c>
       <c r="G160" s="34" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H160" s="20" t="s">
         <v>17</v>
@@ -8791,7 +8789,7 @@
         <v>35</v>
       </c>
       <c r="K160" s="26" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L160" s="12" t="s">
         <v>45</v>
@@ -8808,7 +8806,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D161" s="15" t="s">
         <v>15</v>
@@ -8845,7 +8843,7 @@
         <v>13</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D162" s="29" t="s">
         <v>108</v>
@@ -8879,7 +8877,7 @@
         <v>161.0</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C163" s="14" t="s">
         <v>14</v>
@@ -8916,7 +8914,7 @@
         <v>162.0</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C164" s="14" t="s">
         <v>16</v>
@@ -8937,7 +8935,7 @@
         <v>18</v>
       </c>
       <c r="K164" s="23" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L164" s="18"/>
       <c r="M164" s="19"/>
@@ -8947,7 +8945,7 @@
         <v>163.0</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C165" s="14" t="s">
         <v>20</v>
@@ -8968,7 +8966,7 @@
         <v>18</v>
       </c>
       <c r="K165" s="23" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L165" s="18"/>
       <c r="M165" s="19"/>
@@ -8978,7 +8976,7 @@
         <v>164.0</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C166" s="14" t="s">
         <v>22</v>
@@ -9015,7 +9013,7 @@
         <v>165.0</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C167" s="14" t="s">
         <v>23</v>
@@ -9052,7 +9050,7 @@
         <v>166.0</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C168" s="14" t="s">
         <v>24</v>
@@ -9073,7 +9071,7 @@
         <v>18</v>
       </c>
       <c r="K168" s="23" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L168" s="18"/>
       <c r="M168" s="19"/>
@@ -9083,7 +9081,7 @@
         <v>167.0</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C169" s="14" t="s">
         <v>26</v>
@@ -9104,7 +9102,7 @@
         <v>18</v>
       </c>
       <c r="K169" s="23" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L169" s="18"/>
       <c r="M169" s="19"/>
@@ -9114,7 +9112,7 @@
         <v>168.0</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C170" s="14" t="s">
         <v>28</v>
@@ -9151,7 +9149,7 @@
         <v>169.0</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C171" s="14" t="s">
         <v>29</v>
@@ -9188,40 +9186,40 @@
         <v>170.0</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C172" s="14" t="s">
         <v>30</v>
       </c>
       <c r="D172" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E172" s="39" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F172" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G172" s="39" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H172" s="24" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I172" s="25" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J172" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K172" s="26" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L172" s="12" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M172" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="173">
@@ -9229,40 +9227,40 @@
         <v>171.0</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C173" s="14" t="s">
         <v>39</v>
       </c>
       <c r="D173" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E173" s="39" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F173" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G173" s="39" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H173" s="24" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I173" s="25" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J173" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K173" s="26" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L173" s="12" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M173" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="174" hidden="1">
@@ -9270,7 +9268,7 @@
         <v>172.0</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C174" s="14" t="s">
         <v>44</v>
@@ -9307,7 +9305,7 @@
         <v>173.0</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C175" s="14" t="s">
         <v>45</v>
@@ -9344,40 +9342,40 @@
         <v>174.0</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C176" s="14" t="s">
         <v>46</v>
       </c>
       <c r="D176" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E176" s="39" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F176" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G176" s="39" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H176" s="24" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I176" s="25" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J176" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K176" s="26" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L176" s="12" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M176" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="177">
@@ -9385,40 +9383,40 @@
         <v>175.0</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C177" s="14" t="s">
         <v>52</v>
       </c>
       <c r="D177" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E177" s="39" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F177" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G177" s="39" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="H177" s="24" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I177" s="25" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J177" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K177" s="26" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L177" s="12" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M177" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="178" hidden="1">
@@ -9426,7 +9424,7 @@
         <v>176.0</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C178" s="14" t="s">
         <v>57</v>
@@ -9463,7 +9461,7 @@
         <v>177.0</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C179" s="14" t="s">
         <v>58</v>
@@ -9500,40 +9498,40 @@
         <v>178.0</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C180" s="14" t="s">
         <v>59</v>
       </c>
       <c r="D180" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E180" s="39" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F180" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G180" s="39" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="H180" s="24" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I180" s="25" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J180" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K180" s="26" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L180" s="12" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M180" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="181">
@@ -9541,40 +9539,40 @@
         <v>179.0</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C181" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D181" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E181" s="39" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F181" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G181" s="39" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="H181" s="24" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I181" s="25" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J181" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K181" s="26" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L181" s="12" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M181" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="182" hidden="1">
@@ -9582,7 +9580,7 @@
         <v>180.0</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C182" s="14" t="s">
         <v>70</v>
@@ -9619,7 +9617,7 @@
         <v>181.0</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C183" s="14" t="s">
         <v>71</v>
@@ -9656,7 +9654,7 @@
         <v>182.0</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C184" s="14" t="s">
         <v>72</v>
@@ -9665,25 +9663,25 @@
         <v>84</v>
       </c>
       <c r="E184" s="28" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F184" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G184" s="28" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H184" s="24" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I184" s="25" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J184" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K184" s="26" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L184" s="12" t="s">
         <v>283</v>
@@ -9697,7 +9695,7 @@
         <v>183.0</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C185" s="14" t="s">
         <v>77</v>
@@ -9706,28 +9704,28 @@
         <v>84</v>
       </c>
       <c r="E185" s="28" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F185" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G185" s="28" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="H185" s="24" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I185" s="25" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J185" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K185" s="26" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L185" s="12" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M185" s="14" t="s">
         <v>38</v>
@@ -9738,7 +9736,7 @@
         <v>184.0</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C186" s="14" t="s">
         <v>81</v>
@@ -9775,7 +9773,7 @@
         <v>185.0</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C187" s="14" t="s">
         <v>82</v>
@@ -9812,7 +9810,7 @@
         <v>186.0</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C188" s="14" t="s">
         <v>83</v>
@@ -9821,28 +9819,28 @@
         <v>108</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F188" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G188" s="30" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="H188" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I188" s="25" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J188" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K188" s="26" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L188" s="12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M188" s="14" t="s">
         <v>38</v>
@@ -9853,7 +9851,7 @@
         <v>187.0</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C189" s="14" t="s">
         <v>88</v>
@@ -9862,25 +9860,25 @@
         <v>108</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F189" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G189" s="30" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H189" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I189" s="25" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J189" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K189" s="26" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L189" s="12" t="s">
         <v>272</v>
@@ -9894,7 +9892,7 @@
         <v>188.0</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C190" s="14" t="s">
         <v>92</v>
@@ -9931,7 +9929,7 @@
         <v>189.0</v>
       </c>
       <c r="B191" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C191" s="14" t="s">
         <v>93</v>
@@ -9968,7 +9966,7 @@
         <v>190.0</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C192" s="14" t="s">
         <v>94</v>
@@ -9989,7 +9987,7 @@
         <v>35</v>
       </c>
       <c r="K192" s="26" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L192" s="18"/>
       <c r="M192" s="19"/>
@@ -9999,7 +9997,7 @@
         <v>191.0</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C193" s="14" t="s">
         <v>98</v>
@@ -10020,7 +10018,7 @@
         <v>35</v>
       </c>
       <c r="K193" s="26" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L193" s="18"/>
       <c r="M193" s="19"/>
@@ -10030,7 +10028,7 @@
         <v>192.0</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C194" s="14" t="s">
         <v>101</v>
@@ -10067,7 +10065,7 @@
         <v>193.0</v>
       </c>
       <c r="B195" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C195" s="14" t="s">
         <v>102</v>
@@ -10104,7 +10102,7 @@
         <v>194.0</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C196" s="14" t="s">
         <v>103</v>
@@ -10125,7 +10123,7 @@
         <v>105</v>
       </c>
       <c r="K196" s="23" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L196" s="18"/>
       <c r="M196" s="19"/>
@@ -10135,7 +10133,7 @@
         <v>195.0</v>
       </c>
       <c r="B197" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C197" s="14" t="s">
         <v>107</v>
@@ -10144,25 +10142,25 @@
         <v>108</v>
       </c>
       <c r="E197" s="30" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F197" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G197" s="30" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="H197" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I197" s="30" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="J197" s="29" t="s">
         <v>108</v>
       </c>
       <c r="K197" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L197" s="18"/>
       <c r="M197" s="19"/>
@@ -10172,7 +10170,7 @@
         <v>196.0</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C198" s="14" t="s">
         <v>111</v>
@@ -10209,7 +10207,7 @@
         <v>197.0</v>
       </c>
       <c r="B199" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C199" s="14" t="s">
         <v>112</v>
@@ -10218,25 +10216,25 @@
         <v>108</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F199" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G199" s="30" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="H199" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I199" s="30" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="J199" s="29" t="s">
         <v>108</v>
       </c>
       <c r="K199" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L199" s="18"/>
       <c r="M199" s="19"/>
@@ -10246,7 +10244,7 @@
         <v>198.0</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C200" s="14" t="s">
         <v>113</v>
@@ -10283,7 +10281,7 @@
         <v>199.0</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C201" s="14" t="s">
         <v>114</v>
@@ -10292,19 +10290,19 @@
         <v>108</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F201" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G201" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H201" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I201" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="J201" s="29" t="s">
         <v>108</v>
@@ -10320,7 +10318,7 @@
         <v>200.0</v>
       </c>
       <c r="B202" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C202" s="14" t="s">
         <v>116</v>
@@ -10357,7 +10355,7 @@
         <v>201.0</v>
       </c>
       <c r="B203" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C203" s="14" t="s">
         <v>117</v>
@@ -10366,25 +10364,25 @@
         <v>108</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F203" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G203" s="30" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H203" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I203" s="30" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="J203" s="29" t="s">
         <v>108</v>
       </c>
       <c r="K203" s="32" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L203" s="18"/>
       <c r="M203" s="19"/>
@@ -10394,7 +10392,7 @@
         <v>202.0</v>
       </c>
       <c r="B204" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C204" s="14" t="s">
         <v>119</v>
@@ -10431,7 +10429,7 @@
         <v>203.0</v>
       </c>
       <c r="B205" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C205" s="14" t="s">
         <v>120</v>
@@ -10468,7 +10466,7 @@
         <v>204.0</v>
       </c>
       <c r="B206" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C206" s="14" t="s">
         <v>121</v>
@@ -10489,7 +10487,7 @@
         <v>18</v>
       </c>
       <c r="K206" s="23" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L206" s="18"/>
       <c r="M206" s="19"/>
@@ -10499,7 +10497,7 @@
         <v>205.0</v>
       </c>
       <c r="B207" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C207" s="14" t="s">
         <v>123</v>
@@ -10520,7 +10518,7 @@
         <v>18</v>
       </c>
       <c r="K207" s="23" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L207" s="18"/>
       <c r="M207" s="19"/>
@@ -10530,7 +10528,7 @@
         <v>206.0</v>
       </c>
       <c r="B208" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C208" s="14" t="s">
         <v>125</v>
@@ -10567,7 +10565,7 @@
         <v>207.0</v>
       </c>
       <c r="B209" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C209" s="14" t="s">
         <v>126</v>
@@ -10604,7 +10602,7 @@
         <v>208.0</v>
       </c>
       <c r="B210" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C210" s="14" t="s">
         <v>127</v>
@@ -10618,22 +10616,22 @@
       </c>
       <c r="G210" s="21"/>
       <c r="H210" s="24" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I210" s="25" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="J210" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K210" s="26" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L210" s="12" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M210" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="211">
@@ -10641,7 +10639,7 @@
         <v>209.0</v>
       </c>
       <c r="B211" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C211" s="14" t="s">
         <v>133</v>
@@ -10655,22 +10653,22 @@
       </c>
       <c r="G211" s="21"/>
       <c r="H211" s="24" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I211" s="25" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="J211" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K211" s="26" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L211" s="12" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M211" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="212" hidden="1">
@@ -10678,7 +10676,7 @@
         <v>210.0</v>
       </c>
       <c r="B212" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C212" s="14" t="s">
         <v>138</v>
@@ -10715,40 +10713,40 @@
         <v>211.0</v>
       </c>
       <c r="B213" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C213" s="14" t="s">
         <v>139</v>
       </c>
       <c r="D213" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E213" s="39" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F213" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G213" s="39" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H213" s="24" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I213" s="25" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J213" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K213" s="26" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L213" s="12" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M213" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="214">
@@ -10756,40 +10754,40 @@
         <v>212.0</v>
       </c>
       <c r="B214" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C214" s="14" t="s">
         <v>144</v>
       </c>
       <c r="D214" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E214" s="39" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F214" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G214" s="39" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H214" s="24" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I214" s="25" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J214" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K214" s="26" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L214" s="12" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M214" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="215" hidden="1">
@@ -10797,7 +10795,7 @@
         <v>213.0</v>
       </c>
       <c r="B215" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C215" s="14" t="s">
         <v>149</v>
@@ -10834,40 +10832,40 @@
         <v>214.0</v>
       </c>
       <c r="B216" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C216" s="14" t="s">
         <v>150</v>
       </c>
       <c r="D216" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E216" s="39" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F216" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G216" s="39" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H216" s="24" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I216" s="25" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J216" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K216" s="26" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="L216" s="12" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M216" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="217">
@@ -10875,40 +10873,40 @@
         <v>215.0</v>
       </c>
       <c r="B217" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C217" s="14" t="s">
         <v>155</v>
       </c>
       <c r="D217" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E217" s="39" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F217" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G217" s="39" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H217" s="24" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I217" s="25" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J217" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K217" s="26" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L217" s="12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M217" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="218" hidden="1">
@@ -10916,7 +10914,7 @@
         <v>216.0</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C218" s="14" t="s">
         <v>160</v>
@@ -10953,40 +10951,40 @@
         <v>217.0</v>
       </c>
       <c r="B219" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C219" s="14" t="s">
         <v>161</v>
       </c>
       <c r="D219" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E219" s="39" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F219" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G219" s="39" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H219" s="24" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I219" s="25" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J219" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K219" s="26" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L219" s="12" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M219" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="220">
@@ -10994,40 +10992,40 @@
         <v>218.0</v>
       </c>
       <c r="B220" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C220" s="14" t="s">
         <v>164</v>
       </c>
       <c r="D220" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E220" s="39" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F220" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G220" s="39" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="H220" s="24" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I220" s="25" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J220" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K220" s="26" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L220" s="12" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M220" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="221" hidden="1">
@@ -11035,7 +11033,7 @@
         <v>219.0</v>
       </c>
       <c r="B221" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C221" s="14" t="s">
         <v>167</v>
@@ -11072,34 +11070,34 @@
         <v>220.0</v>
       </c>
       <c r="B222" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C222" s="14" t="s">
         <v>168</v>
       </c>
       <c r="D222" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E222" s="39" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F222" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G222" s="39" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H222" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I222" s="25" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J222" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K222" s="26" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L222" s="12" t="s">
         <v>277</v>
@@ -11113,37 +11111,37 @@
         <v>221.0</v>
       </c>
       <c r="B223" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C223" s="14" t="s">
         <v>174</v>
       </c>
       <c r="D223" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E223" s="39" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F223" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G223" s="39" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H223" s="24" t="s">
         <v>170</v>
       </c>
       <c r="I223" s="25" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J223" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K223" s="26" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L223" s="12" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M223" s="14" t="s">
         <v>38</v>
@@ -11154,7 +11152,7 @@
         <v>222.0</v>
       </c>
       <c r="B224" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C224" s="14" t="s">
         <v>178</v>
@@ -11191,7 +11189,7 @@
         <v>223.0</v>
       </c>
       <c r="B225" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C225" s="14" t="s">
         <v>179</v>
@@ -11200,13 +11198,13 @@
         <v>84</v>
       </c>
       <c r="E225" s="28" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F225" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G225" s="28" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H225" s="20" t="s">
         <v>17</v>
@@ -11216,10 +11214,10 @@
         <v>35</v>
       </c>
       <c r="K225" s="26" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L225" s="12" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M225" s="14" t="s">
         <v>38</v>
@@ -11230,7 +11228,7 @@
         <v>224.0</v>
       </c>
       <c r="B226" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C226" s="14" t="s">
         <v>185</v>
@@ -11239,13 +11237,13 @@
         <v>84</v>
       </c>
       <c r="E226" s="28" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F226" s="27" t="s">
         <v>84</v>
       </c>
       <c r="G226" s="28" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H226" s="20" t="s">
         <v>17</v>
@@ -11255,10 +11253,10 @@
         <v>35</v>
       </c>
       <c r="K226" s="26" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L226" s="12" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M226" s="14" t="s">
         <v>38</v>
@@ -11269,7 +11267,7 @@
         <v>225.0</v>
       </c>
       <c r="B227" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C227" s="14" t="s">
         <v>190</v>
@@ -11306,37 +11304,35 @@
         <v>226.0</v>
       </c>
       <c r="B228" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C228" s="14" t="s">
         <v>191</v>
       </c>
       <c r="D228" s="40" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E228" s="41" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F228" s="40" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G228" s="41" t="s">
-        <v>547</v>
-      </c>
-      <c r="H228" s="40" t="s">
-        <v>546</v>
-      </c>
-      <c r="I228" s="41" t="s">
-        <v>548</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="H228" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I228" s="21"/>
       <c r="J228" s="24" t="s">
         <v>35</v>
       </c>
       <c r="K228" s="26" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L228" s="12" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M228" s="14" t="s">
         <v>38</v>
@@ -11347,29 +11343,27 @@
         <v>227.0</v>
       </c>
       <c r="B229" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C229" s="14" t="s">
         <v>195</v>
       </c>
       <c r="D229" s="40" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E229" s="41" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F229" s="40" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G229" s="41" t="s">
-        <v>551</v>
-      </c>
-      <c r="H229" s="40" t="s">
-        <v>546</v>
-      </c>
-      <c r="I229" s="41" t="s">
         <v>552</v>
       </c>
+      <c r="H229" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I229" s="21"/>
       <c r="J229" s="24" t="s">
         <v>35</v>
       </c>
@@ -11388,7 +11382,7 @@
         <v>228.0</v>
       </c>
       <c r="B230" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C230" s="14" t="s">
         <v>199</v>
@@ -11425,7 +11419,7 @@
         <v>229.0</v>
       </c>
       <c r="B231" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C231" s="14" t="s">
         <v>200</v>
@@ -11456,7 +11450,7 @@
         <v>230.0</v>
       </c>
       <c r="B232" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C232" s="14" t="s">
         <v>203</v>
@@ -11493,7 +11487,7 @@
         <v>231.0</v>
       </c>
       <c r="B233" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C233" s="14" t="s">
         <v>206</v>
@@ -11530,7 +11524,7 @@
         <v>232.0</v>
       </c>
       <c r="B234" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C234" s="14" t="s">
         <v>209</v>
@@ -11561,7 +11555,7 @@
         <v>233.0</v>
       </c>
       <c r="B235" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C235" s="14" t="s">
         <v>212</v>
@@ -11592,7 +11586,7 @@
         <v>234.0</v>
       </c>
       <c r="B236" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C236" s="14" t="s">
         <v>214</v>
@@ -11623,7 +11617,7 @@
         <v>235.0</v>
       </c>
       <c r="B237" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C237" s="14" t="s">
         <v>216</v>
@@ -11654,7 +11648,7 @@
         <v>236.0</v>
       </c>
       <c r="B238" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C238" s="14" t="s">
         <v>219</v>
@@ -11663,19 +11657,19 @@
         <v>108</v>
       </c>
       <c r="E238" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F238" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G238" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H238" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I238" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="J238" s="29" t="s">
         <v>108</v>
@@ -11691,7 +11685,7 @@
         <v>237.0</v>
       </c>
       <c r="B239" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C239" s="14" t="s">
         <v>220</v>
@@ -11728,7 +11722,7 @@
         <v>238.0</v>
       </c>
       <c r="B240" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C240" s="14" t="s">
         <v>221</v>
@@ -11737,19 +11731,19 @@
         <v>108</v>
       </c>
       <c r="E240" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F240" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G240" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H240" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I240" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="J240" s="29" t="s">
         <v>108</v>
@@ -11765,7 +11759,7 @@
         <v>239.0</v>
       </c>
       <c r="B241" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C241" s="14" t="s">
         <v>222</v>
@@ -11802,7 +11796,7 @@
         <v>240.0</v>
       </c>
       <c r="B242" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C242" s="14" t="s">
         <v>223</v>
@@ -11811,19 +11805,19 @@
         <v>108</v>
       </c>
       <c r="E242" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F242" s="29" t="s">
         <v>108</v>
       </c>
       <c r="G242" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H242" s="29" t="s">
         <v>108</v>
       </c>
       <c r="I242" s="30" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="J242" s="29" t="s">
         <v>108</v>
@@ -11839,7 +11833,7 @@
         <v>241.0</v>
       </c>
       <c r="B243" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C243" s="14" t="s">
         <v>224</v>
@@ -11876,7 +11870,7 @@
         <v>242.0</v>
       </c>
       <c r="B244" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C244" s="14" t="s">
         <v>225</v>
@@ -11911,7 +11905,7 @@
         <v>243.0</v>
       </c>
       <c r="B245" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C245" s="14" t="s">
         <v>228</v>
@@ -11946,7 +11940,7 @@
         <v>244.0</v>
       </c>
       <c r="B246" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C246" s="14" t="s">
         <v>230</v>
@@ -11983,7 +11977,7 @@
         <v>245.0</v>
       </c>
       <c r="B247" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C247" s="14" t="s">
         <v>231</v>
@@ -12020,19 +12014,19 @@
         <v>246.0</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C248" s="14" t="s">
         <v>232</v>
       </c>
       <c r="D248" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E248" s="39" t="s">
         <v>567</v>
       </c>
       <c r="F248" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G248" s="39" t="s">
         <v>567</v>
@@ -12053,7 +12047,7 @@
         <v>570</v>
       </c>
       <c r="M248" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="249">
@@ -12061,19 +12055,19 @@
         <v>247.0</v>
       </c>
       <c r="B249" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C249" s="14" t="s">
         <v>237</v>
       </c>
       <c r="D249" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E249" s="39" t="s">
         <v>571</v>
       </c>
       <c r="F249" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G249" s="39" t="s">
         <v>571</v>
@@ -12094,7 +12088,7 @@
         <v>574</v>
       </c>
       <c r="M249" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="250" hidden="1">
@@ -12102,7 +12096,7 @@
         <v>248.0</v>
       </c>
       <c r="B250" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C250" s="14" t="s">
         <v>242</v>
@@ -12139,19 +12133,19 @@
         <v>249.0</v>
       </c>
       <c r="B251" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C251" s="14" t="s">
         <v>243</v>
       </c>
       <c r="D251" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E251" s="39" t="s">
         <v>575</v>
       </c>
       <c r="F251" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G251" s="39" t="s">
         <v>575</v>
@@ -12170,7 +12164,7 @@
         <v>577</v>
       </c>
       <c r="M251" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="252">
@@ -12178,19 +12172,19 @@
         <v>250.0</v>
       </c>
       <c r="B252" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C252" s="14" t="s">
         <v>247</v>
       </c>
       <c r="D252" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E252" s="39" t="s">
         <v>578</v>
       </c>
       <c r="F252" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G252" s="39" t="s">
         <v>578</v>
@@ -12209,7 +12203,7 @@
         <v>580</v>
       </c>
       <c r="M252" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="253" hidden="1">
@@ -12217,7 +12211,7 @@
         <v>251.0</v>
       </c>
       <c r="B253" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C253" s="14" t="s">
         <v>251</v>
@@ -12254,19 +12248,19 @@
         <v>252.0</v>
       </c>
       <c r="B254" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C254" s="14" t="s">
         <v>184</v>
       </c>
       <c r="D254" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E254" s="39" t="s">
         <v>581</v>
       </c>
       <c r="F254" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G254" s="39" t="s">
         <v>581</v>
@@ -12285,7 +12279,7 @@
         <v>583</v>
       </c>
       <c r="M254" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="255">
@@ -12293,19 +12287,19 @@
         <v>253.0</v>
       </c>
       <c r="B255" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C255" s="14" t="s">
         <v>255</v>
       </c>
       <c r="D255" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E255" s="39" t="s">
         <v>584</v>
       </c>
       <c r="F255" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G255" s="39" t="s">
         <v>584</v>
@@ -12324,7 +12318,7 @@
         <v>586</v>
       </c>
       <c r="M255" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="256" hidden="1">
@@ -12332,7 +12326,7 @@
         <v>254.0</v>
       </c>
       <c r="B256" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C256" s="14" t="s">
         <v>259</v>
@@ -12369,19 +12363,19 @@
         <v>255.0</v>
       </c>
       <c r="B257" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C257" s="14" t="s">
         <v>260</v>
       </c>
       <c r="D257" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E257" s="39" t="s">
         <v>587</v>
       </c>
       <c r="F257" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G257" s="39" t="s">
         <v>587</v>
@@ -12400,7 +12394,7 @@
         <v>589</v>
       </c>
       <c r="M257" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="258">
@@ -12408,19 +12402,19 @@
         <v>256.0</v>
       </c>
       <c r="B258" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C258" s="14" t="s">
         <v>56</v>
       </c>
       <c r="D258" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E258" s="39" t="s">
         <v>590</v>
       </c>
       <c r="F258" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G258" s="39" t="s">
         <v>590</v>
@@ -12439,7 +12433,7 @@
         <v>592</v>
       </c>
       <c r="M258" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="259" hidden="1">
@@ -12447,7 +12441,7 @@
         <v>257.0</v>
       </c>
       <c r="B259" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C259" s="14" t="s">
         <v>132</v>
@@ -12484,7 +12478,7 @@
         <v>258.0</v>
       </c>
       <c r="B260" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C260" s="14" t="s">
         <v>264</v>
@@ -12515,7 +12509,7 @@
         <v>595</v>
       </c>
       <c r="M260" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="261">
@@ -12523,7 +12517,7 @@
         <v>259.0</v>
       </c>
       <c r="B261" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C261" s="14" t="s">
         <v>254</v>
@@ -12556,7 +12550,7 @@
         <v>600</v>
       </c>
       <c r="M261" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="262" hidden="1">
@@ -12564,7 +12558,7 @@
         <v>260.0</v>
       </c>
       <c r="B262" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C262" s="14" t="s">
         <v>271</v>
@@ -12601,7 +12595,7 @@
         <v>261.0</v>
       </c>
       <c r="B263" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C263" s="14" t="s">
         <v>272</v>
@@ -12640,7 +12634,7 @@
         <v>262.0</v>
       </c>
       <c r="B264" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C264" s="14" t="s">
         <v>277</v>
@@ -12679,7 +12673,7 @@
         <v>263.0</v>
       </c>
       <c r="B265" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C265" s="14" t="s">
         <v>282</v>
@@ -12716,25 +12710,25 @@
         <v>264.0</v>
       </c>
       <c r="B266" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C266" s="14" t="s">
         <v>283</v>
       </c>
       <c r="D266" s="40" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E266" s="41" t="s">
         <v>607</v>
       </c>
       <c r="F266" s="40" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G266" s="41" t="s">
         <v>607</v>
       </c>
       <c r="H266" s="40" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I266" s="41" t="s">
         <v>607</v>
@@ -12757,7 +12751,7 @@
         <v>265.0</v>
       </c>
       <c r="B267" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C267" s="14" t="s">
         <v>287</v>
@@ -12796,7 +12790,7 @@
         <v>266.0</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C268" s="14" t="s">
         <v>291</v>
@@ -12833,7 +12827,7 @@
         <v>267.0</v>
       </c>
       <c r="B269" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C269" s="14" t="s">
         <v>292</v>
@@ -12872,7 +12866,7 @@
         <v>268.0</v>
       </c>
       <c r="B270" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C270" s="14" t="s">
         <v>295</v>
@@ -12911,7 +12905,7 @@
         <v>269.0</v>
       </c>
       <c r="B271" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C271" s="14" t="s">
         <v>298</v>
@@ -12948,7 +12942,7 @@
         <v>270.0</v>
       </c>
       <c r="B272" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C272" s="14" t="s">
         <v>299</v>
@@ -12989,7 +12983,7 @@
         <v>271.0</v>
       </c>
       <c r="B273" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C273" s="14" t="s">
         <v>303</v>
@@ -13019,7 +13013,7 @@
         <v>622</v>
       </c>
       <c r="L273" s="12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M273" s="14" t="s">
         <v>38</v>
@@ -13030,7 +13024,7 @@
         <v>272.0</v>
       </c>
       <c r="B274" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C274" s="14" t="s">
         <v>307</v>
@@ -13067,7 +13061,7 @@
         <v>273.0</v>
       </c>
       <c r="B275" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C275" s="14" t="s">
         <v>308</v>
@@ -13106,7 +13100,7 @@
         <v>274.0</v>
       </c>
       <c r="B276" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C276" s="14" t="s">
         <v>314</v>
@@ -13145,7 +13139,7 @@
         <v>275.0</v>
       </c>
       <c r="B277" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C277" s="14" t="s">
         <v>319</v>
@@ -13182,7 +13176,7 @@
         <v>276.0</v>
       </c>
       <c r="B278" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C278" s="14" t="s">
         <v>320</v>
@@ -13221,7 +13215,7 @@
         <v>277.0</v>
       </c>
       <c r="B279" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C279" s="14" t="s">
         <v>325</v>
@@ -13262,7 +13256,7 @@
         <v>278.0</v>
       </c>
       <c r="B280" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C280" s="14" t="s">
         <v>330</v>
@@ -13299,7 +13293,7 @@
         <v>279.0</v>
       </c>
       <c r="B281" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C281" s="14" t="s">
         <v>331</v>
@@ -13336,7 +13330,7 @@
         <v>280.0</v>
       </c>
       <c r="B282" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C282" s="14" t="s">
         <v>334</v>
@@ -13373,7 +13367,7 @@
         <v>281.0</v>
       </c>
       <c r="B283" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C283" s="14" t="s">
         <v>335</v>
@@ -13404,7 +13398,7 @@
         <v>282.0</v>
       </c>
       <c r="B284" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C284" s="14" t="s">
         <v>338</v>
@@ -13441,7 +13435,7 @@
         <v>283.0</v>
       </c>
       <c r="B285" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C285" s="14" t="s">
         <v>341</v>
@@ -13478,7 +13472,7 @@
         <v>284.0</v>
       </c>
       <c r="B286" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C286" s="14" t="s">
         <v>342</v>
@@ -13509,7 +13503,7 @@
         <v>641</v>
       </c>
       <c r="M286" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="287">
@@ -13517,7 +13511,7 @@
         <v>285.0</v>
       </c>
       <c r="B287" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C287" s="14" t="s">
         <v>345</v>
@@ -13548,7 +13542,7 @@
         <v>644</v>
       </c>
       <c r="M287" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="288" hidden="1">
@@ -13556,7 +13550,7 @@
         <v>286.0</v>
       </c>
       <c r="B288" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C288" s="14" t="s">
         <v>348</v>
@@ -13593,19 +13587,19 @@
         <v>287.0</v>
       </c>
       <c r="B289" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C289" s="14" t="s">
         <v>349</v>
       </c>
       <c r="D289" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E289" s="39" t="s">
         <v>645</v>
       </c>
       <c r="F289" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G289" s="39" t="s">
         <v>645</v>
@@ -13626,7 +13620,7 @@
         <v>649</v>
       </c>
       <c r="M289" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="290">
@@ -13634,19 +13628,19 @@
         <v>288.0</v>
       </c>
       <c r="B290" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C290" s="14" t="s">
         <v>353</v>
       </c>
       <c r="D290" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E290" s="39" t="s">
         <v>650</v>
       </c>
       <c r="F290" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G290" s="39" t="s">
         <v>650</v>
@@ -13665,7 +13659,7 @@
         <v>652</v>
       </c>
       <c r="M290" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="291" hidden="1">
@@ -13673,7 +13667,7 @@
         <v>289.0</v>
       </c>
       <c r="B291" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C291" s="14" t="s">
         <v>357</v>
@@ -13710,19 +13704,19 @@
         <v>290.0</v>
       </c>
       <c r="B292" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C292" s="14" t="s">
         <v>358</v>
       </c>
       <c r="D292" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E292" s="39" t="s">
         <v>653</v>
       </c>
       <c r="F292" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G292" s="39" t="s">
         <v>653</v>
@@ -13741,7 +13735,7 @@
         <v>655</v>
       </c>
       <c r="M292" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="293">
@@ -13749,19 +13743,19 @@
         <v>291.0</v>
       </c>
       <c r="B293" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C293" s="14" t="s">
         <v>362</v>
       </c>
       <c r="D293" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E293" s="39" t="s">
         <v>656</v>
       </c>
       <c r="F293" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G293" s="39" t="s">
         <v>656</v>
@@ -13780,7 +13774,7 @@
         <v>658</v>
       </c>
       <c r="M293" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="294" hidden="1">
@@ -13788,7 +13782,7 @@
         <v>292.0</v>
       </c>
       <c r="B294" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C294" s="14" t="s">
         <v>365</v>
@@ -13825,19 +13819,19 @@
         <v>293.0</v>
       </c>
       <c r="B295" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C295" s="14" t="s">
         <v>366</v>
       </c>
       <c r="D295" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E295" s="39" t="s">
         <v>659</v>
       </c>
       <c r="F295" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G295" s="39" t="s">
         <v>659</v>
@@ -13856,7 +13850,7 @@
         <v>661</v>
       </c>
       <c r="M295" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="296">
@@ -13864,19 +13858,19 @@
         <v>294.0</v>
       </c>
       <c r="B296" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C296" s="14" t="s">
         <v>369</v>
       </c>
       <c r="D296" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E296" s="39" t="s">
         <v>662</v>
       </c>
       <c r="F296" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G296" s="39" t="s">
         <v>662</v>
@@ -13895,7 +13889,7 @@
         <v>664</v>
       </c>
       <c r="M296" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="297" hidden="1">
@@ -13903,7 +13897,7 @@
         <v>295.0</v>
       </c>
       <c r="B297" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C297" s="14" t="s">
         <v>372</v>
@@ -13940,19 +13934,19 @@
         <v>296.0</v>
       </c>
       <c r="B298" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C298" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D298" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E298" s="39" t="s">
         <v>665</v>
       </c>
       <c r="F298" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G298" s="39" t="s">
         <v>665</v>
@@ -13971,7 +13965,7 @@
         <v>667</v>
       </c>
       <c r="M298" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="299">
@@ -13979,19 +13973,19 @@
         <v>297.0</v>
       </c>
       <c r="B299" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C299" s="14" t="s">
         <v>236</v>
       </c>
       <c r="D299" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E299" s="39" t="s">
         <v>668</v>
       </c>
       <c r="F299" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G299" s="39" t="s">
         <v>668</v>
@@ -14010,7 +14004,7 @@
         <v>670</v>
       </c>
       <c r="M299" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="300" hidden="1">
@@ -14018,7 +14012,7 @@
         <v>298.0</v>
       </c>
       <c r="B300" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C300" s="14" t="s">
         <v>241</v>
@@ -14055,19 +14049,19 @@
         <v>299.0</v>
       </c>
       <c r="B301" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C301" s="14" t="s">
         <v>361</v>
       </c>
       <c r="D301" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E301" s="39" t="s">
         <v>671</v>
       </c>
       <c r="F301" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G301" s="39" t="s">
         <v>671</v>
@@ -14088,7 +14082,7 @@
         <v>675</v>
       </c>
       <c r="M301" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="302">
@@ -14096,19 +14090,19 @@
         <v>300.0</v>
       </c>
       <c r="B302" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C302" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D302" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E302" s="39" t="s">
         <v>676</v>
       </c>
       <c r="F302" s="38" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G302" s="39" t="s">
         <v>676</v>
@@ -14129,7 +14123,7 @@
         <v>679</v>
       </c>
       <c r="M302" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="303" hidden="1">
@@ -14137,10 +14131,10 @@
         <v>301.0</v>
       </c>
       <c r="B303" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C303" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D303" s="15" t="s">
         <v>15</v>
@@ -14174,19 +14168,19 @@
         <v>302.0</v>
       </c>
       <c r="B304" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C304" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D304" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E304" s="39" t="s">
         <v>680</v>
       </c>
       <c r="F304" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G304" s="39" t="s">
         <v>680</v>
@@ -14215,19 +14209,19 @@
         <v>303.0</v>
       </c>
       <c r="B305" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C305" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D305" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E305" s="39" t="s">
         <v>684</v>
       </c>
       <c r="F305" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G305" s="39" t="s">
         <v>684</v>
@@ -14256,10 +14250,10 @@
         <v>304.0</v>
       </c>
       <c r="B306" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C306" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D306" s="15" t="s">
         <v>15</v>
@@ -14293,10 +14287,10 @@
         <v>305.0</v>
       </c>
       <c r="B307" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C307" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D307" s="12" t="s">
         <v>47</v>
@@ -14334,19 +14328,19 @@
         <v>306.0</v>
       </c>
       <c r="B308" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C308" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D308" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E308" s="39" t="s">
         <v>692</v>
       </c>
       <c r="F308" s="38" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G308" s="39" t="s">
         <v>692</v>
@@ -14362,7 +14356,7 @@
         <v>693</v>
       </c>
       <c r="L308" s="12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M308" s="14" t="s">
         <v>38</v>
@@ -14373,10 +14367,10 @@
         <v>307.0</v>
       </c>
       <c r="B309" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C309" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D309" s="15" t="s">
         <v>15</v>
@@ -14410,10 +14404,10 @@
         <v>308.0</v>
       </c>
       <c r="B310" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C310" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D310" s="40" t="s">
         <v>694</v>
@@ -14451,10 +14445,10 @@
         <v>309.0</v>
       </c>
       <c r="B311" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C311" s="14" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D311" s="40" t="s">
         <v>694</v>
@@ -14492,10 +14486,10 @@
         <v>310.0</v>
       </c>
       <c r="B312" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C312" s="14" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D312" s="15" t="s">
         <v>15</v>
@@ -14529,10 +14523,10 @@
         <v>311.0</v>
       </c>
       <c r="B313" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C313" s="14" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D313" s="24" t="s">
         <v>170</v>
@@ -14568,10 +14562,10 @@
         <v>312.0</v>
       </c>
       <c r="B314" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C314" s="14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D314" s="24" t="s">
         <v>170</v>
@@ -14607,10 +14601,10 @@
         <v>313.0</v>
       </c>
       <c r="B315" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C315" s="14" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D315" s="15" t="s">
         <v>15</v>
@@ -14644,10 +14638,10 @@
         <v>314.0</v>
       </c>
       <c r="B316" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C316" s="14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D316" s="35" t="s">
         <v>705</v>
@@ -14681,10 +14675,10 @@
         <v>315.0</v>
       </c>
       <c r="B317" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C317" s="14" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D317" s="35" t="s">
         <v>705</v>
@@ -14718,10 +14712,10 @@
         <v>316.0</v>
       </c>
       <c r="B318" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C318" s="14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D318" s="15" t="s">
         <v>15</v>
@@ -14755,10 +14749,10 @@
         <v>317.0</v>
       </c>
       <c r="B319" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C319" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D319" s="20" t="s">
         <v>17</v>
@@ -14790,10 +14784,10 @@
         <v>318.0</v>
       </c>
       <c r="B320" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C320" s="14" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D320" s="20" t="s">
         <v>17</v>
@@ -14825,10 +14819,10 @@
         <v>319.0</v>
       </c>
       <c r="B321" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="C321" s="14" t="s">
         <v>448</v>
-      </c>
-      <c r="C321" s="14" t="s">
-        <v>446</v>
       </c>
       <c r="D321" s="15" t="s">
         <v>15</v>
@@ -14862,10 +14856,10 @@
         <v>320.0</v>
       </c>
       <c r="B322" s="47" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C322" s="48" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D322" s="49" t="s">
         <v>108</v>
@@ -14906,7 +14900,6 @@
         <filter val="ADC 4"/>
         <filter val="EEPROM"/>
         <filter val="Relay Driver"/>
-        <filter val="PMOD"/>
         <filter val="Slow ADC Ctrl"/>
         <filter val="Present"/>
         <filter val="Timing"/>
